--- a/dataset_tham_dinh_tin_dung.xlsx
+++ b/dataset_tham_dinh_tin_dung.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1017" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="238">
   <si>
     <t>ho_ten</t>
   </si>
@@ -662,606 +662,6 @@
   </si>
   <si>
     <t>Hồ Tuấn Giang</t>
-  </si>
-  <si>
-    <t>056588020201</t>
-  </si>
-  <si>
-    <t>065705016082</t>
-  </si>
-  <si>
-    <t>054592122955</t>
-  </si>
-  <si>
-    <t>009773747216</t>
-  </si>
-  <si>
-    <t>012160878576</t>
-  </si>
-  <si>
-    <t>014940935233</t>
-  </si>
-  <si>
-    <t>070175949293</t>
-  </si>
-  <si>
-    <t>002637242497</t>
-  </si>
-  <si>
-    <t>077116053105</t>
-  </si>
-  <si>
-    <t>042202355940</t>
-  </si>
-  <si>
-    <t>091229484739</t>
-  </si>
-  <si>
-    <t>005486333695</t>
-  </si>
-  <si>
-    <t>024678309633</t>
-  </si>
-  <si>
-    <t>079621428097</t>
-  </si>
-  <si>
-    <t>026155019830</t>
-  </si>
-  <si>
-    <t>066924713216</t>
-  </si>
-  <si>
-    <t>085927046077</t>
-  </si>
-  <si>
-    <t>098938234284</t>
-  </si>
-  <si>
-    <t>075928105973</t>
-  </si>
-  <si>
-    <t>020704108271</t>
-  </si>
-  <si>
-    <t>012258399549</t>
-  </si>
-  <si>
-    <t>012209729510</t>
-  </si>
-  <si>
-    <t>087716046097</t>
-  </si>
-  <si>
-    <t>019113115326</t>
-  </si>
-  <si>
-    <t>066820867467</t>
-  </si>
-  <si>
-    <t>084503902691</t>
-  </si>
-  <si>
-    <t>017434040868</t>
-  </si>
-  <si>
-    <t>025946534967</t>
-  </si>
-  <si>
-    <t>096470629806</t>
-  </si>
-  <si>
-    <t>034609194709</t>
-  </si>
-  <si>
-    <t>012928951476</t>
-  </si>
-  <si>
-    <t>055400717035</t>
-  </si>
-  <si>
-    <t>098504620825</t>
-  </si>
-  <si>
-    <t>016475978345</t>
-  </si>
-  <si>
-    <t>046927038100</t>
-  </si>
-  <si>
-    <t>024856521517</t>
-  </si>
-  <si>
-    <t>068866813964</t>
-  </si>
-  <si>
-    <t>062452353303</t>
-  </si>
-  <si>
-    <t>047986289938</t>
-  </si>
-  <si>
-    <t>010986120272</t>
-  </si>
-  <si>
-    <t>064176337344</t>
-  </si>
-  <si>
-    <t>076107312299</t>
-  </si>
-  <si>
-    <t>069906071392</t>
-  </si>
-  <si>
-    <t>008707511762</t>
-  </si>
-  <si>
-    <t>058453132183</t>
-  </si>
-  <si>
-    <t>062892647402</t>
-  </si>
-  <si>
-    <t>029869152478</t>
-  </si>
-  <si>
-    <t>089340307444</t>
-  </si>
-  <si>
-    <t>006986140994</t>
-  </si>
-  <si>
-    <t>048454713198</t>
-  </si>
-  <si>
-    <t>052334313688</t>
-  </si>
-  <si>
-    <t>059142636617</t>
-  </si>
-  <si>
-    <t>052512040980</t>
-  </si>
-  <si>
-    <t>021563859228</t>
-  </si>
-  <si>
-    <t>029843355286</t>
-  </si>
-  <si>
-    <t>057449357407</t>
-  </si>
-  <si>
-    <t>015308152485</t>
-  </si>
-  <si>
-    <t>093111222889</t>
-  </si>
-  <si>
-    <t>024290932666</t>
-  </si>
-  <si>
-    <t>077913575960</t>
-  </si>
-  <si>
-    <t>040641597279</t>
-  </si>
-  <si>
-    <t>071319237070</t>
-  </si>
-  <si>
-    <t>000533342205</t>
-  </si>
-  <si>
-    <t>097419358057</t>
-  </si>
-  <si>
-    <t>037625805073</t>
-  </si>
-  <si>
-    <t>083261542864</t>
-  </si>
-  <si>
-    <t>093166883900</t>
-  </si>
-  <si>
-    <t>094232042478</t>
-  </si>
-  <si>
-    <t>081835218649</t>
-  </si>
-  <si>
-    <t>020931404983</t>
-  </si>
-  <si>
-    <t>049453634651</t>
-  </si>
-  <si>
-    <t>057136228365</t>
-  </si>
-  <si>
-    <t>039462826183</t>
-  </si>
-  <si>
-    <t>066218165442</t>
-  </si>
-  <si>
-    <t>075224789046</t>
-  </si>
-  <si>
-    <t>006388442045</t>
-  </si>
-  <si>
-    <t>080400700139</t>
-  </si>
-  <si>
-    <t>030332027568</t>
-  </si>
-  <si>
-    <t>069644421015</t>
-  </si>
-  <si>
-    <t>087301242997</t>
-  </si>
-  <si>
-    <t>051195373814</t>
-  </si>
-  <si>
-    <t>082915491286</t>
-  </si>
-  <si>
-    <t>050304026417</t>
-  </si>
-  <si>
-    <t>009481049162</t>
-  </si>
-  <si>
-    <t>008403522804</t>
-  </si>
-  <si>
-    <t>096960139148</t>
-  </si>
-  <si>
-    <t>052144513223</t>
-  </si>
-  <si>
-    <t>055708987143</t>
-  </si>
-  <si>
-    <t>021526703563</t>
-  </si>
-  <si>
-    <t>024149743368</t>
-  </si>
-  <si>
-    <t>010837827971</t>
-  </si>
-  <si>
-    <t>079457772521</t>
-  </si>
-  <si>
-    <t>040495722434</t>
-  </si>
-  <si>
-    <t>031973212144</t>
-  </si>
-  <si>
-    <t>017637655075</t>
-  </si>
-  <si>
-    <t>023546775733</t>
-  </si>
-  <si>
-    <t>084937982571</t>
-  </si>
-  <si>
-    <t>011893087728</t>
-  </si>
-  <si>
-    <t>045964946346</t>
-  </si>
-  <si>
-    <t>013487968721</t>
-  </si>
-  <si>
-    <t>004379863312</t>
-  </si>
-  <si>
-    <t>006254934576</t>
-  </si>
-  <si>
-    <t>091816209707</t>
-  </si>
-  <si>
-    <t>071169692476</t>
-  </si>
-  <si>
-    <t>096312724391</t>
-  </si>
-  <si>
-    <t>064877723145</t>
-  </si>
-  <si>
-    <t>061388660706</t>
-  </si>
-  <si>
-    <t>003557373622</t>
-  </si>
-  <si>
-    <t>005638094737</t>
-  </si>
-  <si>
-    <t>063273780372</t>
-  </si>
-  <si>
-    <t>021638170736</t>
-  </si>
-  <si>
-    <t>032894543008</t>
-  </si>
-  <si>
-    <t>014162938468</t>
-  </si>
-  <si>
-    <t>074257218539</t>
-  </si>
-  <si>
-    <t>061998946672</t>
-  </si>
-  <si>
-    <t>044611350615</t>
-  </si>
-  <si>
-    <t>034995099046</t>
-  </si>
-  <si>
-    <t>080981216131</t>
-  </si>
-  <si>
-    <t>076647470762</t>
-  </si>
-  <si>
-    <t>013455711187</t>
-  </si>
-  <si>
-    <t>040463018962</t>
-  </si>
-  <si>
-    <t>089584969951</t>
-  </si>
-  <si>
-    <t>077675325305</t>
-  </si>
-  <si>
-    <t>053783970194</t>
-  </si>
-  <si>
-    <t>061206059510</t>
-  </si>
-  <si>
-    <t>078508412451</t>
-  </si>
-  <si>
-    <t>028809013564</t>
-  </si>
-  <si>
-    <t>070388198918</t>
-  </si>
-  <si>
-    <t>022771461180</t>
-  </si>
-  <si>
-    <t>091192544947</t>
-  </si>
-  <si>
-    <t>028290594946</t>
-  </si>
-  <si>
-    <t>003667820806</t>
-  </si>
-  <si>
-    <t>041238178391</t>
-  </si>
-  <si>
-    <t>028405291306</t>
-  </si>
-  <si>
-    <t>043996479451</t>
-  </si>
-  <si>
-    <t>063641797266</t>
-  </si>
-  <si>
-    <t>063488751094</t>
-  </si>
-  <si>
-    <t>030471032736</t>
-  </si>
-  <si>
-    <t>074994170269</t>
-  </si>
-  <si>
-    <t>079964499783</t>
-  </si>
-  <si>
-    <t>018579166430</t>
-  </si>
-  <si>
-    <t>088718516880</t>
-  </si>
-  <si>
-    <t>054260743757</t>
-  </si>
-  <si>
-    <t>073760416009</t>
-  </si>
-  <si>
-    <t>061321009434</t>
-  </si>
-  <si>
-    <t>050110846676</t>
-  </si>
-  <si>
-    <t>041674347243</t>
-  </si>
-  <si>
-    <t>036972997914</t>
-  </si>
-  <si>
-    <t>025723633930</t>
-  </si>
-  <si>
-    <t>033122992171</t>
-  </si>
-  <si>
-    <t>026237421120</t>
-  </si>
-  <si>
-    <t>030395830755</t>
-  </si>
-  <si>
-    <t>050780851356</t>
-  </si>
-  <si>
-    <t>036500443984</t>
-  </si>
-  <si>
-    <t>071986819856</t>
-  </si>
-  <si>
-    <t>032577650961</t>
-  </si>
-  <si>
-    <t>050419696050</t>
-  </si>
-  <si>
-    <t>094314619798</t>
-  </si>
-  <si>
-    <t>017504451704</t>
-  </si>
-  <si>
-    <t>034351419330</t>
-  </si>
-  <si>
-    <t>098935673556</t>
-  </si>
-  <si>
-    <t>009934358005</t>
-  </si>
-  <si>
-    <t>009776766620</t>
-  </si>
-  <si>
-    <t>042781275410</t>
-  </si>
-  <si>
-    <t>025972794419</t>
-  </si>
-  <si>
-    <t>093203667447</t>
-  </si>
-  <si>
-    <t>011943346286</t>
-  </si>
-  <si>
-    <t>047930121873</t>
-  </si>
-  <si>
-    <t>047734745167</t>
-  </si>
-  <si>
-    <t>036882455336</t>
-  </si>
-  <si>
-    <t>034723501571</t>
-  </si>
-  <si>
-    <t>055127136780</t>
-  </si>
-  <si>
-    <t>074683557915</t>
-  </si>
-  <si>
-    <t>019974863158</t>
-  </si>
-  <si>
-    <t>072989325966</t>
-  </si>
-  <si>
-    <t>007452954600</t>
-  </si>
-  <si>
-    <t>029336456636</t>
-  </si>
-  <si>
-    <t>036600035891</t>
-  </si>
-  <si>
-    <t>053868267154</t>
-  </si>
-  <si>
-    <t>028188429108</t>
-  </si>
-  <si>
-    <t>004234947329</t>
-  </si>
-  <si>
-    <t>004401943791</t>
-  </si>
-  <si>
-    <t>054650660306</t>
-  </si>
-  <si>
-    <t>090538403877</t>
-  </si>
-  <si>
-    <t>010161758771</t>
-  </si>
-  <si>
-    <t>043780508727</t>
-  </si>
-  <si>
-    <t>034691600564</t>
-  </si>
-  <si>
-    <t>054711146399</t>
-  </si>
-  <si>
-    <t>026431409147</t>
-  </si>
-  <si>
-    <t>082795255224</t>
-  </si>
-  <si>
-    <t>054678188252</t>
-  </si>
-  <si>
-    <t>045714342785</t>
-  </si>
-  <si>
-    <t>061362631151</t>
-  </si>
-  <si>
-    <t>032111157492</t>
-  </si>
-  <si>
-    <t>092364564423</t>
-  </si>
-  <si>
-    <t>061653679973</t>
-  </si>
-  <si>
-    <t>065601825146</t>
-  </si>
-  <si>
-    <t>019417521610</t>
-  </si>
-  <si>
-    <t>040943061437</t>
-  </si>
-  <si>
-    <t>077699447068</t>
   </si>
   <si>
     <t>Hai Bà Trưng, Hà Nội</t>
@@ -1719,23 +1119,23 @@
       <c r="A2" t="s">
         <v>17</v>
       </c>
-      <c r="B2" t="s">
-        <v>216</v>
+      <c r="B2">
+        <v>56588020201</v>
       </c>
       <c r="C2">
         <v>49</v>
       </c>
       <c r="D2" t="s">
-        <v>416</v>
+        <v>216</v>
       </c>
       <c r="E2" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F2">
         <v>29000000</v>
       </c>
       <c r="G2" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H2">
         <v>10000000</v>
@@ -1772,23 +1172,23 @@
       <c r="A3" t="s">
         <v>18</v>
       </c>
-      <c r="B3" t="s">
-        <v>217</v>
+      <c r="B3">
+        <v>65705016082</v>
       </c>
       <c r="C3">
         <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>417</v>
+        <v>217</v>
       </c>
       <c r="E3" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F3">
         <v>50000000</v>
       </c>
       <c r="G3" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H3">
         <v>30000000</v>
@@ -1825,26 +1225,32 @@
       <c r="A4" t="s">
         <v>19</v>
       </c>
-      <c r="B4" t="s">
-        <v>218</v>
+      <c r="B4">
+        <v>54592122955</v>
       </c>
       <c r="C4">
         <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>418</v>
+        <v>218</v>
       </c>
       <c r="E4" t="s">
-        <v>433</v>
+        <v>233</v>
       </c>
       <c r="F4">
         <v>3000000</v>
       </c>
       <c r="G4" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H4">
         <v>40000000</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
       </c>
       <c r="K4">
         <v>0</v>
@@ -1872,23 +1278,23 @@
       <c r="A5" t="s">
         <v>20</v>
       </c>
-      <c r="B5" t="s">
-        <v>219</v>
+      <c r="B5">
+        <v>9773747216</v>
       </c>
       <c r="C5">
         <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>418</v>
+        <v>218</v>
       </c>
       <c r="E5" t="s">
-        <v>434</v>
+        <v>234</v>
       </c>
       <c r="F5">
         <v>16000000</v>
       </c>
       <c r="G5" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H5">
         <v>20000000</v>
@@ -1925,23 +1331,23 @@
       <c r="A6" t="s">
         <v>21</v>
       </c>
-      <c r="B6" t="s">
-        <v>220</v>
+      <c r="B6">
+        <v>12160878576</v>
       </c>
       <c r="C6">
         <v>52</v>
       </c>
       <c r="D6" t="s">
-        <v>419</v>
+        <v>219</v>
       </c>
       <c r="E6" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F6">
         <v>30000000</v>
       </c>
       <c r="G6" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H6">
         <v>40000000</v>
@@ -1978,23 +1384,23 @@
       <c r="A7" t="s">
         <v>22</v>
       </c>
-      <c r="B7" t="s">
-        <v>221</v>
+      <c r="B7">
+        <v>14940935233</v>
       </c>
       <c r="C7">
         <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>420</v>
+        <v>220</v>
       </c>
       <c r="E7" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F7">
         <v>33000000</v>
       </c>
       <c r="G7" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H7">
         <v>35000000</v>
@@ -2031,23 +1437,23 @@
       <c r="A8" t="s">
         <v>23</v>
       </c>
-      <c r="B8" t="s">
-        <v>222</v>
+      <c r="B8">
+        <v>70175949293</v>
       </c>
       <c r="C8">
         <v>50</v>
       </c>
       <c r="D8" t="s">
-        <v>421</v>
+        <v>221</v>
       </c>
       <c r="E8" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F8">
         <v>16000000</v>
       </c>
       <c r="G8" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H8">
         <v>20000000</v>
@@ -2084,23 +1490,23 @@
       <c r="A9" t="s">
         <v>24</v>
       </c>
-      <c r="B9" t="s">
-        <v>223</v>
+      <c r="B9">
+        <v>2637242497</v>
       </c>
       <c r="C9">
         <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>418</v>
+        <v>218</v>
       </c>
       <c r="E9" t="s">
-        <v>434</v>
+        <v>234</v>
       </c>
       <c r="F9">
         <v>4000000</v>
       </c>
       <c r="G9" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H9">
         <v>40000000</v>
@@ -2137,23 +1543,23 @@
       <c r="A10" t="s">
         <v>25</v>
       </c>
-      <c r="B10" t="s">
-        <v>224</v>
+      <c r="B10">
+        <v>77116053105</v>
       </c>
       <c r="C10">
         <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>422</v>
+        <v>222</v>
       </c>
       <c r="E10" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F10">
         <v>26000000</v>
       </c>
       <c r="G10" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H10">
         <v>40000000</v>
@@ -2190,23 +1596,23 @@
       <c r="A11" t="s">
         <v>26</v>
       </c>
-      <c r="B11" t="s">
-        <v>225</v>
+      <c r="B11">
+        <v>42202355940</v>
       </c>
       <c r="C11">
         <v>54</v>
       </c>
       <c r="D11" t="s">
-        <v>421</v>
+        <v>221</v>
       </c>
       <c r="E11" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F11">
         <v>23000000</v>
       </c>
       <c r="G11" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H11">
         <v>10000000</v>
@@ -2243,23 +1649,23 @@
       <c r="A12" t="s">
         <v>27</v>
       </c>
-      <c r="B12" t="s">
-        <v>226</v>
+      <c r="B12">
+        <v>91229484739</v>
       </c>
       <c r="C12">
         <v>53</v>
       </c>
       <c r="D12" t="s">
-        <v>423</v>
+        <v>223</v>
       </c>
       <c r="E12" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F12">
         <v>30000000</v>
       </c>
       <c r="G12" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H12">
         <v>25000000</v>
@@ -2296,23 +1702,23 @@
       <c r="A13" t="s">
         <v>28</v>
       </c>
-      <c r="B13" t="s">
-        <v>227</v>
+      <c r="B13">
+        <v>5486333695</v>
       </c>
       <c r="C13">
         <v>40</v>
       </c>
       <c r="D13" t="s">
-        <v>424</v>
+        <v>224</v>
       </c>
       <c r="E13" t="s">
-        <v>434</v>
+        <v>234</v>
       </c>
       <c r="F13">
         <v>6000000</v>
       </c>
       <c r="G13" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H13">
         <v>40000000</v>
@@ -2349,23 +1755,23 @@
       <c r="A14" t="s">
         <v>29</v>
       </c>
-      <c r="B14" t="s">
-        <v>228</v>
+      <c r="B14">
+        <v>24678309633</v>
       </c>
       <c r="C14">
         <v>54</v>
       </c>
       <c r="D14" t="s">
-        <v>424</v>
+        <v>224</v>
       </c>
       <c r="E14" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F14">
         <v>10000000</v>
       </c>
       <c r="G14" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H14">
         <v>35000000</v>
@@ -2402,23 +1808,23 @@
       <c r="A15" t="s">
         <v>30</v>
       </c>
-      <c r="B15" t="s">
-        <v>229</v>
+      <c r="B15">
+        <v>79621428097</v>
       </c>
       <c r="C15">
         <v>44</v>
       </c>
       <c r="D15" t="s">
-        <v>420</v>
+        <v>220</v>
       </c>
       <c r="E15" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F15">
         <v>47000000</v>
       </c>
       <c r="G15" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H15">
         <v>35000000</v>
@@ -2455,23 +1861,23 @@
       <c r="A16" t="s">
         <v>31</v>
       </c>
-      <c r="B16" t="s">
-        <v>230</v>
+      <c r="B16">
+        <v>26155019830</v>
       </c>
       <c r="C16">
         <v>37</v>
       </c>
       <c r="D16" t="s">
-        <v>416</v>
+        <v>216</v>
       </c>
       <c r="E16" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F16">
         <v>14000000</v>
       </c>
       <c r="G16" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H16">
         <v>20000000</v>
@@ -2508,23 +1914,23 @@
       <c r="A17" t="s">
         <v>32</v>
       </c>
-      <c r="B17" t="s">
-        <v>231</v>
+      <c r="B17">
+        <v>66924713216</v>
       </c>
       <c r="C17">
         <v>39</v>
       </c>
       <c r="D17" t="s">
-        <v>425</v>
+        <v>225</v>
       </c>
       <c r="E17" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F17">
         <v>19000000</v>
       </c>
       <c r="G17" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H17">
         <v>15000000</v>
@@ -2561,23 +1967,23 @@
       <c r="A18" t="s">
         <v>33</v>
       </c>
-      <c r="B18" t="s">
-        <v>232</v>
+      <c r="B18">
+        <v>85927046077</v>
       </c>
       <c r="C18">
         <v>54</v>
       </c>
       <c r="D18" t="s">
-        <v>426</v>
+        <v>226</v>
       </c>
       <c r="E18" t="s">
-        <v>434</v>
+        <v>234</v>
       </c>
       <c r="F18">
         <v>23000000</v>
       </c>
       <c r="G18" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H18">
         <v>25000000</v>
@@ -2614,23 +2020,23 @@
       <c r="A19" t="s">
         <v>34</v>
       </c>
-      <c r="B19" t="s">
-        <v>233</v>
+      <c r="B19">
+        <v>98938234284</v>
       </c>
       <c r="C19">
         <v>26</v>
       </c>
       <c r="D19" t="s">
-        <v>427</v>
+        <v>227</v>
       </c>
       <c r="E19" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F19">
         <v>33000000</v>
       </c>
       <c r="G19" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H19">
         <v>10000000</v>
@@ -2667,23 +2073,23 @@
       <c r="A20" t="s">
         <v>35</v>
       </c>
-      <c r="B20" t="s">
-        <v>234</v>
+      <c r="B20">
+        <v>75928105973</v>
       </c>
       <c r="C20">
         <v>40</v>
       </c>
       <c r="D20" t="s">
-        <v>421</v>
+        <v>221</v>
       </c>
       <c r="E20" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F20">
         <v>16000000</v>
       </c>
       <c r="G20" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H20">
         <v>35000000</v>
@@ -2720,23 +2126,23 @@
       <c r="A21" t="s">
         <v>36</v>
       </c>
-      <c r="B21" t="s">
-        <v>235</v>
+      <c r="B21">
+        <v>20704108271</v>
       </c>
       <c r="C21">
         <v>34</v>
       </c>
       <c r="D21" t="s">
-        <v>428</v>
+        <v>228</v>
       </c>
       <c r="E21" t="s">
-        <v>434</v>
+        <v>234</v>
       </c>
       <c r="F21">
         <v>23000000</v>
       </c>
       <c r="G21" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H21">
         <v>15000000</v>
@@ -2773,26 +2179,32 @@
       <c r="A22" t="s">
         <v>37</v>
       </c>
-      <c r="B22" t="s">
-        <v>236</v>
+      <c r="B22">
+        <v>12258399549</v>
       </c>
       <c r="C22">
         <v>19</v>
       </c>
       <c r="D22" t="s">
-        <v>429</v>
+        <v>229</v>
       </c>
       <c r="E22" t="s">
-        <v>433</v>
+        <v>233</v>
       </c>
       <c r="F22">
         <v>6000000</v>
       </c>
       <c r="G22" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H22">
         <v>40000000</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -2820,23 +2232,23 @@
       <c r="A23" t="s">
         <v>38</v>
       </c>
-      <c r="B23" t="s">
-        <v>237</v>
+      <c r="B23">
+        <v>12209729510</v>
       </c>
       <c r="C23">
         <v>42</v>
       </c>
       <c r="D23" t="s">
-        <v>417</v>
+        <v>217</v>
       </c>
       <c r="E23" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F23">
         <v>24000000</v>
       </c>
       <c r="G23" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H23">
         <v>25000000</v>
@@ -2873,23 +2285,23 @@
       <c r="A24" t="s">
         <v>39</v>
       </c>
-      <c r="B24" t="s">
-        <v>238</v>
+      <c r="B24">
+        <v>87716046097</v>
       </c>
       <c r="C24">
         <v>48</v>
       </c>
       <c r="D24" t="s">
-        <v>417</v>
+        <v>217</v>
       </c>
       <c r="E24" t="s">
-        <v>433</v>
+        <v>233</v>
       </c>
       <c r="F24">
         <v>12000000</v>
       </c>
       <c r="G24" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H24">
         <v>40000000</v>
@@ -2926,23 +2338,23 @@
       <c r="A25" t="s">
         <v>40</v>
       </c>
-      <c r="B25" t="s">
-        <v>239</v>
+      <c r="B25">
+        <v>19113115326</v>
       </c>
       <c r="C25">
         <v>33</v>
       </c>
       <c r="D25" t="s">
-        <v>423</v>
+        <v>223</v>
       </c>
       <c r="E25" t="s">
-        <v>434</v>
+        <v>234</v>
       </c>
       <c r="F25">
         <v>28000000</v>
       </c>
       <c r="G25" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H25">
         <v>35000000</v>
@@ -2979,23 +2391,23 @@
       <c r="A26" t="s">
         <v>41</v>
       </c>
-      <c r="B26" t="s">
-        <v>240</v>
+      <c r="B26">
+        <v>66820867467</v>
       </c>
       <c r="C26">
         <v>53</v>
       </c>
       <c r="D26" t="s">
-        <v>417</v>
+        <v>217</v>
       </c>
       <c r="E26" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F26">
         <v>25000000</v>
       </c>
       <c r="G26" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H26">
         <v>35000000</v>
@@ -3032,23 +2444,23 @@
       <c r="A27" t="s">
         <v>42</v>
       </c>
-      <c r="B27" t="s">
-        <v>241</v>
+      <c r="B27">
+        <v>84503902691</v>
       </c>
       <c r="C27">
         <v>50</v>
       </c>
       <c r="D27" t="s">
-        <v>425</v>
+        <v>225</v>
       </c>
       <c r="E27" t="s">
-        <v>434</v>
+        <v>234</v>
       </c>
       <c r="F27">
         <v>12000000</v>
       </c>
       <c r="G27" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H27">
         <v>10000000</v>
@@ -3085,23 +2497,23 @@
       <c r="A28" t="s">
         <v>43</v>
       </c>
-      <c r="B28" t="s">
-        <v>242</v>
+      <c r="B28">
+        <v>17434040868</v>
       </c>
       <c r="C28">
         <v>48</v>
       </c>
       <c r="D28" t="s">
-        <v>430</v>
+        <v>230</v>
       </c>
       <c r="E28" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F28">
         <v>31000000</v>
       </c>
       <c r="G28" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H28">
         <v>15000000</v>
@@ -3138,23 +2550,23 @@
       <c r="A29" t="s">
         <v>44</v>
       </c>
-      <c r="B29" t="s">
-        <v>243</v>
+      <c r="B29">
+        <v>25946534967</v>
       </c>
       <c r="C29">
         <v>28</v>
       </c>
       <c r="D29" t="s">
-        <v>416</v>
+        <v>216</v>
       </c>
       <c r="E29" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F29">
         <v>21000000</v>
       </c>
       <c r="G29" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H29">
         <v>15000000</v>
@@ -3191,23 +2603,23 @@
       <c r="A30" t="s">
         <v>45</v>
       </c>
-      <c r="B30" t="s">
-        <v>244</v>
+      <c r="B30">
+        <v>96470629806</v>
       </c>
       <c r="C30">
         <v>37</v>
       </c>
       <c r="D30" t="s">
-        <v>431</v>
+        <v>231</v>
       </c>
       <c r="E30" t="s">
-        <v>433</v>
+        <v>233</v>
       </c>
       <c r="F30">
         <v>15000000</v>
       </c>
       <c r="G30" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H30">
         <v>20000000</v>
@@ -3244,23 +2656,23 @@
       <c r="A31" t="s">
         <v>46</v>
       </c>
-      <c r="B31" t="s">
-        <v>245</v>
+      <c r="B31">
+        <v>34609194709</v>
       </c>
       <c r="C31">
         <v>46</v>
       </c>
       <c r="D31" t="s">
-        <v>423</v>
+        <v>223</v>
       </c>
       <c r="E31" t="s">
-        <v>434</v>
+        <v>234</v>
       </c>
       <c r="F31">
         <v>23000000</v>
       </c>
       <c r="G31" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H31">
         <v>25000000</v>
@@ -3297,23 +2709,23 @@
       <c r="A32" t="s">
         <v>47</v>
       </c>
-      <c r="B32" t="s">
-        <v>246</v>
+      <c r="B32">
+        <v>12928951476</v>
       </c>
       <c r="C32">
         <v>40</v>
       </c>
       <c r="D32" t="s">
-        <v>431</v>
+        <v>231</v>
       </c>
       <c r="E32" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F32">
         <v>17000000</v>
       </c>
       <c r="G32" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H32">
         <v>10000000</v>
@@ -3350,23 +2762,23 @@
       <c r="A33" t="s">
         <v>48</v>
       </c>
-      <c r="B33" t="s">
-        <v>247</v>
+      <c r="B33">
+        <v>55400717035</v>
       </c>
       <c r="C33">
         <v>29</v>
       </c>
       <c r="D33" t="s">
-        <v>420</v>
+        <v>220</v>
       </c>
       <c r="E33" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F33">
         <v>15000000</v>
       </c>
       <c r="G33" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H33">
         <v>30000000</v>
@@ -3403,23 +2815,23 @@
       <c r="A34" t="s">
         <v>49</v>
       </c>
-      <c r="B34" t="s">
-        <v>248</v>
+      <c r="B34">
+        <v>98504620825</v>
       </c>
       <c r="C34">
         <v>37</v>
       </c>
       <c r="D34" t="s">
-        <v>424</v>
+        <v>224</v>
       </c>
       <c r="E34" t="s">
-        <v>434</v>
+        <v>234</v>
       </c>
       <c r="F34">
         <v>10000000</v>
       </c>
       <c r="G34" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H34">
         <v>30000000</v>
@@ -3456,23 +2868,23 @@
       <c r="A35" t="s">
         <v>50</v>
       </c>
-      <c r="B35" t="s">
-        <v>249</v>
+      <c r="B35">
+        <v>16475978345</v>
       </c>
       <c r="C35">
         <v>53</v>
       </c>
       <c r="D35" t="s">
-        <v>423</v>
+        <v>223</v>
       </c>
       <c r="E35" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F35">
         <v>24000000</v>
       </c>
       <c r="G35" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H35">
         <v>20000000</v>
@@ -3509,23 +2921,23 @@
       <c r="A36" t="s">
         <v>51</v>
       </c>
-      <c r="B36" t="s">
-        <v>250</v>
+      <c r="B36">
+        <v>46927038100</v>
       </c>
       <c r="C36">
         <v>33</v>
       </c>
       <c r="D36" t="s">
-        <v>430</v>
+        <v>230</v>
       </c>
       <c r="E36" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F36">
         <v>31000000</v>
       </c>
       <c r="G36" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H36">
         <v>40000000</v>
@@ -3562,23 +2974,23 @@
       <c r="A37" t="s">
         <v>52</v>
       </c>
-      <c r="B37" t="s">
-        <v>251</v>
+      <c r="B37">
+        <v>24856521517</v>
       </c>
       <c r="C37">
         <v>51</v>
       </c>
       <c r="D37" t="s">
-        <v>421</v>
+        <v>221</v>
       </c>
       <c r="E37" t="s">
-        <v>434</v>
+        <v>234</v>
       </c>
       <c r="F37">
         <v>12000000</v>
       </c>
       <c r="G37" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H37">
         <v>25000000</v>
@@ -3615,23 +3027,23 @@
       <c r="A38" t="s">
         <v>53</v>
       </c>
-      <c r="B38" t="s">
-        <v>252</v>
+      <c r="B38">
+        <v>68866813964</v>
       </c>
       <c r="C38">
         <v>40</v>
       </c>
       <c r="D38" t="s">
-        <v>419</v>
+        <v>219</v>
       </c>
       <c r="E38" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F38">
         <v>28000000</v>
       </c>
       <c r="G38" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H38">
         <v>35000000</v>
@@ -3668,23 +3080,23 @@
       <c r="A39" t="s">
         <v>54</v>
       </c>
-      <c r="B39" t="s">
-        <v>253</v>
+      <c r="B39">
+        <v>62452353303</v>
       </c>
       <c r="C39">
         <v>24</v>
       </c>
       <c r="D39" t="s">
-        <v>424</v>
+        <v>224</v>
       </c>
       <c r="E39" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F39">
         <v>17000000</v>
       </c>
       <c r="G39" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H39">
         <v>10000000</v>
@@ -3721,23 +3133,23 @@
       <c r="A40" t="s">
         <v>55</v>
       </c>
-      <c r="B40" t="s">
-        <v>254</v>
+      <c r="B40">
+        <v>47986289938</v>
       </c>
       <c r="C40">
         <v>44</v>
       </c>
       <c r="D40" t="s">
-        <v>428</v>
+        <v>228</v>
       </c>
       <c r="E40" t="s">
-        <v>433</v>
+        <v>233</v>
       </c>
       <c r="F40">
         <v>4000000</v>
       </c>
       <c r="G40" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H40">
         <v>35000000</v>
@@ -3774,23 +3186,23 @@
       <c r="A41" t="s">
         <v>56</v>
       </c>
-      <c r="B41" t="s">
-        <v>255</v>
+      <c r="B41">
+        <v>10986120272</v>
       </c>
       <c r="C41">
         <v>33</v>
       </c>
       <c r="D41" t="s">
-        <v>422</v>
+        <v>222</v>
       </c>
       <c r="E41" t="s">
-        <v>434</v>
+        <v>234</v>
       </c>
       <c r="F41">
         <v>14000000</v>
       </c>
       <c r="G41" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H41">
         <v>40000000</v>
@@ -3827,23 +3239,23 @@
       <c r="A42" t="s">
         <v>57</v>
       </c>
-      <c r="B42" t="s">
-        <v>256</v>
+      <c r="B42">
+        <v>64176337344</v>
       </c>
       <c r="C42">
         <v>41</v>
       </c>
       <c r="D42" t="s">
-        <v>425</v>
+        <v>225</v>
       </c>
       <c r="E42" t="s">
-        <v>434</v>
+        <v>234</v>
       </c>
       <c r="F42">
         <v>26000000</v>
       </c>
       <c r="G42" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H42">
         <v>35000000</v>
@@ -3880,23 +3292,23 @@
       <c r="A43" t="s">
         <v>58</v>
       </c>
-      <c r="B43" t="s">
-        <v>257</v>
+      <c r="B43">
+        <v>76107312299</v>
       </c>
       <c r="C43">
         <v>47</v>
       </c>
       <c r="D43" t="s">
-        <v>419</v>
+        <v>219</v>
       </c>
       <c r="E43" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F43">
         <v>50000000</v>
       </c>
       <c r="G43" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H43">
         <v>10000000</v>
@@ -3933,23 +3345,23 @@
       <c r="A44" t="s">
         <v>59</v>
       </c>
-      <c r="B44" t="s">
-        <v>258</v>
+      <c r="B44">
+        <v>69906071392</v>
       </c>
       <c r="C44">
         <v>45</v>
       </c>
       <c r="D44" t="s">
-        <v>429</v>
+        <v>229</v>
       </c>
       <c r="E44" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F44">
         <v>39000000</v>
       </c>
       <c r="G44" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H44">
         <v>10000000</v>
@@ -3986,23 +3398,23 @@
       <c r="A45" t="s">
         <v>60</v>
       </c>
-      <c r="B45" t="s">
-        <v>259</v>
+      <c r="B45">
+        <v>8707511762</v>
       </c>
       <c r="C45">
         <v>38</v>
       </c>
       <c r="D45" t="s">
-        <v>419</v>
+        <v>219</v>
       </c>
       <c r="E45" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F45">
         <v>50000000</v>
       </c>
       <c r="G45" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H45">
         <v>10000000</v>
@@ -4039,23 +3451,23 @@
       <c r="A46" t="s">
         <v>61</v>
       </c>
-      <c r="B46" t="s">
-        <v>260</v>
+      <c r="B46">
+        <v>58453132183</v>
       </c>
       <c r="C46">
         <v>53</v>
       </c>
       <c r="D46" t="s">
-        <v>429</v>
+        <v>229</v>
       </c>
       <c r="E46" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F46">
         <v>4000000</v>
       </c>
       <c r="G46" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H46">
         <v>20000000</v>
@@ -4092,23 +3504,23 @@
       <c r="A47" t="s">
         <v>62</v>
       </c>
-      <c r="B47" t="s">
-        <v>261</v>
+      <c r="B47">
+        <v>62892647402</v>
       </c>
       <c r="C47">
         <v>38</v>
       </c>
       <c r="D47" t="s">
-        <v>423</v>
+        <v>223</v>
       </c>
       <c r="E47" t="s">
-        <v>434</v>
+        <v>234</v>
       </c>
       <c r="F47">
         <v>19000000</v>
       </c>
       <c r="G47" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H47">
         <v>40000000</v>
@@ -4145,23 +3557,23 @@
       <c r="A48" t="s">
         <v>63</v>
       </c>
-      <c r="B48" t="s">
-        <v>262</v>
+      <c r="B48">
+        <v>29869152478</v>
       </c>
       <c r="C48">
         <v>33</v>
       </c>
       <c r="D48" t="s">
-        <v>428</v>
+        <v>228</v>
       </c>
       <c r="E48" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F48">
         <v>10000000</v>
       </c>
       <c r="G48" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H48">
         <v>40000000</v>
@@ -4198,23 +3610,23 @@
       <c r="A49" t="s">
         <v>64</v>
       </c>
-      <c r="B49" t="s">
-        <v>263</v>
+      <c r="B49">
+        <v>89340307444</v>
       </c>
       <c r="C49">
         <v>39</v>
       </c>
       <c r="D49" t="s">
-        <v>422</v>
+        <v>222</v>
       </c>
       <c r="E49" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F49">
         <v>31000000</v>
       </c>
       <c r="G49" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H49">
         <v>35000000</v>
@@ -4251,23 +3663,23 @@
       <c r="A50" t="s">
         <v>65</v>
       </c>
-      <c r="B50" t="s">
-        <v>264</v>
+      <c r="B50">
+        <v>6986140994</v>
       </c>
       <c r="C50">
         <v>32</v>
       </c>
       <c r="D50" t="s">
-        <v>424</v>
+        <v>224</v>
       </c>
       <c r="E50" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F50">
         <v>20000000</v>
       </c>
       <c r="G50" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H50">
         <v>20000000</v>
@@ -4304,23 +3716,23 @@
       <c r="A51" t="s">
         <v>30</v>
       </c>
-      <c r="B51" t="s">
-        <v>265</v>
+      <c r="B51">
+        <v>48454713198</v>
       </c>
       <c r="C51">
         <v>37</v>
       </c>
       <c r="D51" t="s">
-        <v>427</v>
+        <v>227</v>
       </c>
       <c r="E51" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F51">
         <v>17000000</v>
       </c>
       <c r="G51" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H51">
         <v>25000000</v>
@@ -4357,23 +3769,23 @@
       <c r="A52" t="s">
         <v>66</v>
       </c>
-      <c r="B52" t="s">
-        <v>266</v>
+      <c r="B52">
+        <v>52334313688</v>
       </c>
       <c r="C52">
         <v>34</v>
       </c>
       <c r="D52" t="s">
-        <v>421</v>
+        <v>221</v>
       </c>
       <c r="E52" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F52">
         <v>24000000</v>
       </c>
       <c r="G52" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H52">
         <v>40000000</v>
@@ -4410,23 +3822,23 @@
       <c r="A53" t="s">
         <v>67</v>
       </c>
-      <c r="B53" t="s">
-        <v>267</v>
+      <c r="B53">
+        <v>59142636617</v>
       </c>
       <c r="C53">
         <v>28</v>
       </c>
       <c r="D53" t="s">
-        <v>431</v>
+        <v>231</v>
       </c>
       <c r="E53" t="s">
-        <v>433</v>
+        <v>233</v>
       </c>
       <c r="F53">
         <v>8000000</v>
       </c>
       <c r="G53" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H53">
         <v>25000000</v>
@@ -4463,23 +3875,23 @@
       <c r="A54" t="s">
         <v>68</v>
       </c>
-      <c r="B54" t="s">
-        <v>268</v>
+      <c r="B54">
+        <v>52512040980</v>
       </c>
       <c r="C54">
         <v>52</v>
       </c>
       <c r="D54" t="s">
-        <v>427</v>
+        <v>227</v>
       </c>
       <c r="E54" t="s">
-        <v>433</v>
+        <v>233</v>
       </c>
       <c r="F54">
         <v>13000000</v>
       </c>
       <c r="G54" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H54">
         <v>15000000</v>
@@ -4516,23 +3928,23 @@
       <c r="A55" t="s">
         <v>69</v>
       </c>
-      <c r="B55" t="s">
-        <v>269</v>
+      <c r="B55">
+        <v>21563859228</v>
       </c>
       <c r="C55">
         <v>44</v>
       </c>
       <c r="D55" t="s">
-        <v>419</v>
+        <v>219</v>
       </c>
       <c r="E55" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F55">
         <v>36000000</v>
       </c>
       <c r="G55" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H55">
         <v>20000000</v>
@@ -4569,23 +3981,23 @@
       <c r="A56" t="s">
         <v>70</v>
       </c>
-      <c r="B56" t="s">
-        <v>270</v>
+      <c r="B56">
+        <v>29843355286</v>
       </c>
       <c r="C56">
         <v>27</v>
       </c>
       <c r="D56" t="s">
-        <v>426</v>
+        <v>226</v>
       </c>
       <c r="E56" t="s">
-        <v>434</v>
+        <v>234</v>
       </c>
       <c r="F56">
         <v>14000000</v>
       </c>
       <c r="G56" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H56">
         <v>25000000</v>
@@ -4622,23 +4034,23 @@
       <c r="A57" t="s">
         <v>71</v>
       </c>
-      <c r="B57" t="s">
-        <v>271</v>
+      <c r="B57">
+        <v>57449357407</v>
       </c>
       <c r="C57">
         <v>42</v>
       </c>
       <c r="D57" t="s">
-        <v>418</v>
+        <v>218</v>
       </c>
       <c r="E57" t="s">
-        <v>433</v>
+        <v>233</v>
       </c>
       <c r="F57">
         <v>13000000</v>
       </c>
       <c r="G57" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H57">
         <v>10000000</v>
@@ -4675,23 +4087,23 @@
       <c r="A58" t="s">
         <v>72</v>
       </c>
-      <c r="B58" t="s">
-        <v>272</v>
+      <c r="B58">
+        <v>15308152485</v>
       </c>
       <c r="C58">
         <v>51</v>
       </c>
       <c r="D58" t="s">
-        <v>425</v>
+        <v>225</v>
       </c>
       <c r="E58" t="s">
-        <v>433</v>
+        <v>233</v>
       </c>
       <c r="F58">
         <v>16000000</v>
       </c>
       <c r="G58" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H58">
         <v>25000000</v>
@@ -4728,23 +4140,23 @@
       <c r="A59" t="s">
         <v>73</v>
       </c>
-      <c r="B59" t="s">
-        <v>273</v>
+      <c r="B59">
+        <v>93111222889</v>
       </c>
       <c r="C59">
         <v>49</v>
       </c>
       <c r="D59" t="s">
-        <v>425</v>
+        <v>225</v>
       </c>
       <c r="E59" t="s">
-        <v>434</v>
+        <v>234</v>
       </c>
       <c r="F59">
         <v>10000000</v>
       </c>
       <c r="G59" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H59">
         <v>40000000</v>
@@ -4781,23 +4193,23 @@
       <c r="A60" t="s">
         <v>74</v>
       </c>
-      <c r="B60" t="s">
-        <v>274</v>
+      <c r="B60">
+        <v>24290932666</v>
       </c>
       <c r="C60">
         <v>39</v>
       </c>
       <c r="D60" t="s">
-        <v>418</v>
+        <v>218</v>
       </c>
       <c r="E60" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F60">
         <v>47000000</v>
       </c>
       <c r="G60" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H60">
         <v>35000000</v>
@@ -4834,23 +4246,23 @@
       <c r="A61" t="s">
         <v>75</v>
       </c>
-      <c r="B61" t="s">
-        <v>275</v>
+      <c r="B61">
+        <v>77913575960</v>
       </c>
       <c r="C61">
         <v>51</v>
       </c>
       <c r="D61" t="s">
-        <v>422</v>
+        <v>222</v>
       </c>
       <c r="E61" t="s">
-        <v>434</v>
+        <v>234</v>
       </c>
       <c r="F61">
         <v>11000000</v>
       </c>
       <c r="G61" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H61">
         <v>30000000</v>
@@ -4887,23 +4299,23 @@
       <c r="A62" t="s">
         <v>76</v>
       </c>
-      <c r="B62" t="s">
-        <v>276</v>
+      <c r="B62">
+        <v>40641597279</v>
       </c>
       <c r="C62">
         <v>53</v>
       </c>
       <c r="D62" t="s">
-        <v>419</v>
+        <v>219</v>
       </c>
       <c r="E62" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F62">
         <v>27000000</v>
       </c>
       <c r="G62" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H62">
         <v>10000000</v>
@@ -4940,23 +4352,23 @@
       <c r="A63" t="s">
         <v>77</v>
       </c>
-      <c r="B63" t="s">
-        <v>277</v>
+      <c r="B63">
+        <v>71319237070</v>
       </c>
       <c r="C63">
         <v>27</v>
       </c>
       <c r="D63" t="s">
-        <v>430</v>
+        <v>230</v>
       </c>
       <c r="E63" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F63">
         <v>45000000</v>
       </c>
       <c r="G63" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H63">
         <v>15000000</v>
@@ -4993,23 +4405,23 @@
       <c r="A64" t="s">
         <v>78</v>
       </c>
-      <c r="B64" t="s">
-        <v>278</v>
+      <c r="B64">
+        <v>533342205</v>
       </c>
       <c r="C64">
         <v>54</v>
       </c>
       <c r="D64" t="s">
-        <v>416</v>
+        <v>216</v>
       </c>
       <c r="E64" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F64">
         <v>23000000</v>
       </c>
       <c r="G64" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H64">
         <v>20000000</v>
@@ -5046,23 +4458,23 @@
       <c r="A65" t="s">
         <v>79</v>
       </c>
-      <c r="B65" t="s">
-        <v>279</v>
+      <c r="B65">
+        <v>97419358057</v>
       </c>
       <c r="C65">
         <v>42</v>
       </c>
       <c r="D65" t="s">
-        <v>422</v>
+        <v>222</v>
       </c>
       <c r="E65" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F65">
         <v>15000000</v>
       </c>
       <c r="G65" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H65">
         <v>25000000</v>
@@ -5099,23 +4511,23 @@
       <c r="A66" t="s">
         <v>80</v>
       </c>
-      <c r="B66" t="s">
-        <v>280</v>
+      <c r="B66">
+        <v>37625805073</v>
       </c>
       <c r="C66">
         <v>47</v>
       </c>
       <c r="D66" t="s">
-        <v>416</v>
+        <v>216</v>
       </c>
       <c r="E66" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F66">
         <v>23000000</v>
       </c>
       <c r="G66" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H66">
         <v>15000000</v>
@@ -5152,23 +4564,23 @@
       <c r="A67" t="s">
         <v>81</v>
       </c>
-      <c r="B67" t="s">
-        <v>281</v>
+      <c r="B67">
+        <v>83261542864</v>
       </c>
       <c r="C67">
         <v>37</v>
       </c>
       <c r="D67" t="s">
-        <v>418</v>
+        <v>218</v>
       </c>
       <c r="E67" t="s">
-        <v>434</v>
+        <v>234</v>
       </c>
       <c r="F67">
         <v>9000000</v>
       </c>
       <c r="G67" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H67">
         <v>35000000</v>
@@ -5205,23 +4617,23 @@
       <c r="A68" t="s">
         <v>82</v>
       </c>
-      <c r="B68" t="s">
-        <v>282</v>
+      <c r="B68">
+        <v>93166883900</v>
       </c>
       <c r="C68">
         <v>24</v>
       </c>
       <c r="D68" t="s">
-        <v>423</v>
+        <v>223</v>
       </c>
       <c r="E68" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F68">
         <v>22000000</v>
       </c>
       <c r="G68" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H68">
         <v>20000000</v>
@@ -5258,23 +4670,23 @@
       <c r="A69" t="s">
         <v>83</v>
       </c>
-      <c r="B69" t="s">
-        <v>283</v>
+      <c r="B69">
+        <v>94232042478</v>
       </c>
       <c r="C69">
         <v>35</v>
       </c>
       <c r="D69" t="s">
-        <v>425</v>
+        <v>225</v>
       </c>
       <c r="E69" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F69">
         <v>20000000</v>
       </c>
       <c r="G69" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H69">
         <v>25000000</v>
@@ -5311,23 +4723,23 @@
       <c r="A70" t="s">
         <v>84</v>
       </c>
-      <c r="B70" t="s">
-        <v>284</v>
+      <c r="B70">
+        <v>81835218649</v>
       </c>
       <c r="C70">
         <v>35</v>
       </c>
       <c r="D70" t="s">
-        <v>421</v>
+        <v>221</v>
       </c>
       <c r="E70" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F70">
         <v>19000000</v>
       </c>
       <c r="G70" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H70">
         <v>30000000</v>
@@ -5364,23 +4776,23 @@
       <c r="A71" t="s">
         <v>85</v>
       </c>
-      <c r="B71" t="s">
-        <v>285</v>
+      <c r="B71">
+        <v>20931404983</v>
       </c>
       <c r="C71">
         <v>38</v>
       </c>
       <c r="D71" t="s">
-        <v>429</v>
+        <v>229</v>
       </c>
       <c r="E71" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F71">
         <v>51000000</v>
       </c>
       <c r="G71" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H71">
         <v>10000000</v>
@@ -5417,23 +4829,23 @@
       <c r="A72" t="s">
         <v>86</v>
       </c>
-      <c r="B72" t="s">
-        <v>286</v>
+      <c r="B72">
+        <v>49453634651</v>
       </c>
       <c r="C72">
         <v>53</v>
       </c>
       <c r="D72" t="s">
-        <v>416</v>
+        <v>216</v>
       </c>
       <c r="E72" t="s">
-        <v>434</v>
+        <v>234</v>
       </c>
       <c r="F72">
         <v>17000000</v>
       </c>
       <c r="G72" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H72">
         <v>25000000</v>
@@ -5470,23 +4882,23 @@
       <c r="A73" t="s">
         <v>87</v>
       </c>
-      <c r="B73" t="s">
-        <v>287</v>
+      <c r="B73">
+        <v>57136228365</v>
       </c>
       <c r="C73">
         <v>38</v>
       </c>
       <c r="D73" t="s">
-        <v>424</v>
+        <v>224</v>
       </c>
       <c r="E73" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F73">
         <v>51000000</v>
       </c>
       <c r="G73" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H73">
         <v>30000000</v>
@@ -5523,23 +4935,23 @@
       <c r="A74" t="s">
         <v>88</v>
       </c>
-      <c r="B74" t="s">
-        <v>288</v>
+      <c r="B74">
+        <v>39462826183</v>
       </c>
       <c r="C74">
         <v>41</v>
       </c>
       <c r="D74" t="s">
-        <v>428</v>
+        <v>228</v>
       </c>
       <c r="E74" t="s">
-        <v>434</v>
+        <v>234</v>
       </c>
       <c r="F74">
         <v>12000000</v>
       </c>
       <c r="G74" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H74">
         <v>25000000</v>
@@ -5576,26 +4988,32 @@
       <c r="A75" t="s">
         <v>89</v>
       </c>
-      <c r="B75" t="s">
-        <v>289</v>
+      <c r="B75">
+        <v>66218165442</v>
       </c>
       <c r="C75">
         <v>19</v>
       </c>
       <c r="D75" t="s">
-        <v>416</v>
+        <v>216</v>
       </c>
       <c r="E75" t="s">
-        <v>433</v>
+        <v>233</v>
       </c>
       <c r="F75">
         <v>3000000</v>
       </c>
       <c r="G75" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H75">
         <v>35000000</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
       </c>
       <c r="K75">
         <v>0</v>
@@ -5623,23 +5041,23 @@
       <c r="A76" t="s">
         <v>90</v>
       </c>
-      <c r="B76" t="s">
-        <v>290</v>
+      <c r="B76">
+        <v>75224789046</v>
       </c>
       <c r="C76">
         <v>33</v>
       </c>
       <c r="D76" t="s">
-        <v>425</v>
+        <v>225</v>
       </c>
       <c r="E76" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F76">
         <v>57000000</v>
       </c>
       <c r="G76" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H76">
         <v>30000000</v>
@@ -5676,23 +5094,23 @@
       <c r="A77" t="s">
         <v>91</v>
       </c>
-      <c r="B77" t="s">
-        <v>291</v>
+      <c r="B77">
+        <v>6388442045</v>
       </c>
       <c r="C77">
         <v>55</v>
       </c>
       <c r="D77" t="s">
-        <v>428</v>
+        <v>228</v>
       </c>
       <c r="E77" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F77">
         <v>19000000</v>
       </c>
       <c r="G77" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H77">
         <v>35000000</v>
@@ -5729,23 +5147,23 @@
       <c r="A78" t="s">
         <v>92</v>
       </c>
-      <c r="B78" t="s">
-        <v>292</v>
+      <c r="B78">
+        <v>80400700139</v>
       </c>
       <c r="C78">
         <v>31</v>
       </c>
       <c r="D78" t="s">
-        <v>426</v>
+        <v>226</v>
       </c>
       <c r="E78" t="s">
-        <v>433</v>
+        <v>233</v>
       </c>
       <c r="F78">
         <v>14000000</v>
       </c>
       <c r="G78" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H78">
         <v>25000000</v>
@@ -5782,23 +5200,23 @@
       <c r="A79" t="s">
         <v>93</v>
       </c>
-      <c r="B79" t="s">
-        <v>293</v>
+      <c r="B79">
+        <v>30332027568</v>
       </c>
       <c r="C79">
         <v>42</v>
       </c>
       <c r="D79" t="s">
-        <v>421</v>
+        <v>221</v>
       </c>
       <c r="E79" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F79">
         <v>17000000</v>
       </c>
       <c r="G79" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H79">
         <v>10000000</v>
@@ -5835,23 +5253,23 @@
       <c r="A80" t="s">
         <v>94</v>
       </c>
-      <c r="B80" t="s">
-        <v>294</v>
+      <c r="B80">
+        <v>69644421015</v>
       </c>
       <c r="C80">
         <v>27</v>
       </c>
       <c r="D80" t="s">
-        <v>425</v>
+        <v>225</v>
       </c>
       <c r="E80" t="s">
-        <v>433</v>
+        <v>233</v>
       </c>
       <c r="F80">
         <v>10000000</v>
       </c>
       <c r="G80" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H80">
         <v>40000000</v>
@@ -5888,23 +5306,23 @@
       <c r="A81" t="s">
         <v>95</v>
       </c>
-      <c r="B81" t="s">
-        <v>295</v>
+      <c r="B81">
+        <v>87301242997</v>
       </c>
       <c r="C81">
         <v>38</v>
       </c>
       <c r="D81" t="s">
-        <v>425</v>
+        <v>225</v>
       </c>
       <c r="E81" t="s">
-        <v>434</v>
+        <v>234</v>
       </c>
       <c r="F81">
         <v>16000000</v>
       </c>
       <c r="G81" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H81">
         <v>35000000</v>
@@ -5941,23 +5359,23 @@
       <c r="A82" t="s">
         <v>96</v>
       </c>
-      <c r="B82" t="s">
-        <v>296</v>
+      <c r="B82">
+        <v>51195373814</v>
       </c>
       <c r="C82">
         <v>45</v>
       </c>
       <c r="D82" t="s">
-        <v>428</v>
+        <v>228</v>
       </c>
       <c r="E82" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F82">
         <v>50000000</v>
       </c>
       <c r="G82" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H82">
         <v>20000000</v>
@@ -5994,23 +5412,23 @@
       <c r="A83" t="s">
         <v>97</v>
       </c>
-      <c r="B83" t="s">
-        <v>297</v>
+      <c r="B83">
+        <v>82915491286</v>
       </c>
       <c r="C83">
         <v>53</v>
       </c>
       <c r="D83" t="s">
-        <v>426</v>
+        <v>226</v>
       </c>
       <c r="E83" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F83">
         <v>19000000</v>
       </c>
       <c r="G83" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H83">
         <v>25000000</v>
@@ -6047,23 +5465,23 @@
       <c r="A84" t="s">
         <v>98</v>
       </c>
-      <c r="B84" t="s">
-        <v>298</v>
+      <c r="B84">
+        <v>50304026417</v>
       </c>
       <c r="C84">
         <v>26</v>
       </c>
       <c r="D84" t="s">
-        <v>417</v>
+        <v>217</v>
       </c>
       <c r="E84" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F84">
         <v>27000000</v>
       </c>
       <c r="G84" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H84">
         <v>10000000</v>
@@ -6100,23 +5518,23 @@
       <c r="A85" t="s">
         <v>99</v>
       </c>
-      <c r="B85" t="s">
-        <v>299</v>
+      <c r="B85">
+        <v>9481049162</v>
       </c>
       <c r="C85">
         <v>41</v>
       </c>
       <c r="D85" t="s">
-        <v>431</v>
+        <v>231</v>
       </c>
       <c r="E85" t="s">
-        <v>434</v>
+        <v>234</v>
       </c>
       <c r="F85">
         <v>22000000</v>
       </c>
       <c r="G85" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H85">
         <v>35000000</v>
@@ -6153,23 +5571,23 @@
       <c r="A86" t="s">
         <v>100</v>
       </c>
-      <c r="B86" t="s">
-        <v>300</v>
+      <c r="B86">
+        <v>8403522804</v>
       </c>
       <c r="C86">
         <v>29</v>
       </c>
       <c r="D86" t="s">
-        <v>419</v>
+        <v>219</v>
       </c>
       <c r="E86" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F86">
         <v>31000000</v>
       </c>
       <c r="G86" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H86">
         <v>15000000</v>
@@ -6206,23 +5624,23 @@
       <c r="A87" t="s">
         <v>101</v>
       </c>
-      <c r="B87" t="s">
-        <v>301</v>
+      <c r="B87">
+        <v>96960139148</v>
       </c>
       <c r="C87">
         <v>38</v>
       </c>
       <c r="D87" t="s">
-        <v>416</v>
+        <v>216</v>
       </c>
       <c r="E87" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F87">
         <v>23000000</v>
       </c>
       <c r="G87" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H87">
         <v>35000000</v>
@@ -6259,23 +5677,23 @@
       <c r="A88" t="s">
         <v>102</v>
       </c>
-      <c r="B88" t="s">
-        <v>302</v>
+      <c r="B88">
+        <v>52144513223</v>
       </c>
       <c r="C88">
         <v>72</v>
       </c>
       <c r="D88" t="s">
-        <v>419</v>
+        <v>219</v>
       </c>
       <c r="E88" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F88">
         <v>20000000</v>
       </c>
       <c r="G88" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H88">
         <v>25000000</v>
@@ -6312,23 +5730,23 @@
       <c r="A89" t="s">
         <v>103</v>
       </c>
-      <c r="B89" t="s">
-        <v>303</v>
+      <c r="B89">
+        <v>55708987143</v>
       </c>
       <c r="C89">
         <v>26</v>
       </c>
       <c r="D89" t="s">
-        <v>417</v>
+        <v>217</v>
       </c>
       <c r="E89" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F89">
         <v>25000000</v>
       </c>
       <c r="G89" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H89">
         <v>35000000</v>
@@ -6365,23 +5783,23 @@
       <c r="A90" t="s">
         <v>104</v>
       </c>
-      <c r="B90" t="s">
-        <v>304</v>
+      <c r="B90">
+        <v>21526703563</v>
       </c>
       <c r="C90">
         <v>38</v>
       </c>
       <c r="D90" t="s">
-        <v>427</v>
+        <v>227</v>
       </c>
       <c r="E90" t="s">
-        <v>434</v>
+        <v>234</v>
       </c>
       <c r="F90">
         <v>9000000</v>
       </c>
       <c r="G90" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H90">
         <v>15000000</v>
@@ -6418,23 +5836,23 @@
       <c r="A91" t="s">
         <v>105</v>
       </c>
-      <c r="B91" t="s">
-        <v>305</v>
+      <c r="B91">
+        <v>24149743368</v>
       </c>
       <c r="C91">
         <v>71</v>
       </c>
       <c r="D91" t="s">
-        <v>425</v>
+        <v>225</v>
       </c>
       <c r="E91" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F91">
         <v>16000000</v>
       </c>
       <c r="G91" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H91">
         <v>25000000</v>
@@ -6471,23 +5889,23 @@
       <c r="A92" t="s">
         <v>106</v>
       </c>
-      <c r="B92" t="s">
-        <v>306</v>
+      <c r="B92">
+        <v>10837827971</v>
       </c>
       <c r="C92">
         <v>40</v>
       </c>
       <c r="D92" t="s">
-        <v>423</v>
+        <v>223</v>
       </c>
       <c r="E92" t="s">
-        <v>434</v>
+        <v>234</v>
       </c>
       <c r="F92">
         <v>19000000</v>
       </c>
       <c r="G92" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H92">
         <v>40000000</v>
@@ -6524,23 +5942,23 @@
       <c r="A93" t="s">
         <v>107</v>
       </c>
-      <c r="B93" t="s">
-        <v>307</v>
+      <c r="B93">
+        <v>79457772521</v>
       </c>
       <c r="C93">
         <v>42</v>
       </c>
       <c r="D93" t="s">
-        <v>417</v>
+        <v>217</v>
       </c>
       <c r="E93" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F93">
         <v>7000000</v>
       </c>
       <c r="G93" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H93">
         <v>15000000</v>
@@ -6577,23 +5995,23 @@
       <c r="A94" t="s">
         <v>108</v>
       </c>
-      <c r="B94" t="s">
-        <v>308</v>
+      <c r="B94">
+        <v>40495722434</v>
       </c>
       <c r="C94">
         <v>49</v>
       </c>
       <c r="D94" t="s">
-        <v>420</v>
+        <v>220</v>
       </c>
       <c r="E94" t="s">
-        <v>434</v>
+        <v>234</v>
       </c>
       <c r="F94">
         <v>18000000</v>
       </c>
       <c r="G94" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H94">
         <v>20000000</v>
@@ -6630,23 +6048,23 @@
       <c r="A95" t="s">
         <v>109</v>
       </c>
-      <c r="B95" t="s">
-        <v>309</v>
+      <c r="B95">
+        <v>31973212144</v>
       </c>
       <c r="C95">
         <v>72</v>
       </c>
       <c r="D95" t="s">
-        <v>427</v>
+        <v>227</v>
       </c>
       <c r="E95" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F95">
         <v>21000000</v>
       </c>
       <c r="G95" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H95">
         <v>35000000</v>
@@ -6683,23 +6101,23 @@
       <c r="A96" t="s">
         <v>110</v>
       </c>
-      <c r="B96" t="s">
-        <v>310</v>
+      <c r="B96">
+        <v>17637655075</v>
       </c>
       <c r="C96">
         <v>71</v>
       </c>
       <c r="D96" t="s">
-        <v>421</v>
+        <v>221</v>
       </c>
       <c r="E96" t="s">
-        <v>433</v>
+        <v>233</v>
       </c>
       <c r="F96">
         <v>12000000</v>
       </c>
       <c r="G96" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H96">
         <v>40000000</v>
@@ -6736,23 +6154,23 @@
       <c r="A97" t="s">
         <v>111</v>
       </c>
-      <c r="B97" t="s">
-        <v>311</v>
+      <c r="B97">
+        <v>23546775733</v>
       </c>
       <c r="C97">
         <v>38</v>
       </c>
       <c r="D97" t="s">
-        <v>417</v>
+        <v>217</v>
       </c>
       <c r="E97" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F97">
         <v>12000000</v>
       </c>
       <c r="G97" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H97">
         <v>25000000</v>
@@ -6789,23 +6207,23 @@
       <c r="A98" t="s">
         <v>112</v>
       </c>
-      <c r="B98" t="s">
-        <v>312</v>
+      <c r="B98">
+        <v>84937982571</v>
       </c>
       <c r="C98">
         <v>54</v>
       </c>
       <c r="D98" t="s">
-        <v>430</v>
+        <v>230</v>
       </c>
       <c r="E98" t="s">
-        <v>433</v>
+        <v>233</v>
       </c>
       <c r="F98">
         <v>22000000</v>
       </c>
       <c r="G98" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H98">
         <v>35000000</v>
@@ -6842,23 +6260,23 @@
       <c r="A99" t="s">
         <v>113</v>
       </c>
-      <c r="B99" t="s">
-        <v>313</v>
+      <c r="B99">
+        <v>11893087728</v>
       </c>
       <c r="C99">
         <v>31</v>
       </c>
       <c r="D99" t="s">
-        <v>416</v>
+        <v>216</v>
       </c>
       <c r="E99" t="s">
-        <v>433</v>
+        <v>233</v>
       </c>
       <c r="F99">
         <v>13000000</v>
       </c>
       <c r="G99" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H99">
         <v>30000000</v>
@@ -6895,23 +6313,23 @@
       <c r="A100" t="s">
         <v>114</v>
       </c>
-      <c r="B100" t="s">
-        <v>314</v>
+      <c r="B100">
+        <v>45964946346</v>
       </c>
       <c r="C100">
         <v>53</v>
       </c>
       <c r="D100" t="s">
-        <v>427</v>
+        <v>227</v>
       </c>
       <c r="E100" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F100">
         <v>9000000</v>
       </c>
       <c r="G100" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H100">
         <v>10000000</v>
@@ -6948,23 +6366,23 @@
       <c r="A101" t="s">
         <v>115</v>
       </c>
-      <c r="B101" t="s">
-        <v>315</v>
+      <c r="B101">
+        <v>13487968721</v>
       </c>
       <c r="C101">
         <v>25</v>
       </c>
       <c r="D101" t="s">
-        <v>422</v>
+        <v>222</v>
       </c>
       <c r="E101" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F101">
         <v>4000000</v>
       </c>
       <c r="G101" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H101">
         <v>40000000</v>
@@ -7001,23 +6419,23 @@
       <c r="A102" t="s">
         <v>116</v>
       </c>
-      <c r="B102" t="s">
-        <v>316</v>
+      <c r="B102">
+        <v>4379863312</v>
       </c>
       <c r="C102">
         <v>48</v>
       </c>
       <c r="D102" t="s">
-        <v>426</v>
+        <v>226</v>
       </c>
       <c r="E102" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F102">
         <v>23000000</v>
       </c>
       <c r="G102" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H102">
         <v>40000000</v>
@@ -7054,23 +6472,23 @@
       <c r="A103" t="s">
         <v>117</v>
       </c>
-      <c r="B103" t="s">
-        <v>317</v>
+      <c r="B103">
+        <v>6254934576</v>
       </c>
       <c r="C103">
         <v>33</v>
       </c>
       <c r="D103" t="s">
-        <v>421</v>
+        <v>221</v>
       </c>
       <c r="E103" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F103">
         <v>18000000</v>
       </c>
       <c r="G103" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H103">
         <v>35000000</v>
@@ -7107,23 +6525,23 @@
       <c r="A104" t="s">
         <v>118</v>
       </c>
-      <c r="B104" t="s">
-        <v>318</v>
+      <c r="B104">
+        <v>91816209707</v>
       </c>
       <c r="C104">
         <v>41</v>
       </c>
       <c r="D104" t="s">
-        <v>419</v>
+        <v>219</v>
       </c>
       <c r="E104" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F104">
         <v>24000000</v>
       </c>
       <c r="G104" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H104">
         <v>25000000</v>
@@ -7160,23 +6578,23 @@
       <c r="A105" t="s">
         <v>119</v>
       </c>
-      <c r="B105" t="s">
-        <v>319</v>
+      <c r="B105">
+        <v>71169692476</v>
       </c>
       <c r="C105">
         <v>48</v>
       </c>
       <c r="D105" t="s">
-        <v>423</v>
+        <v>223</v>
       </c>
       <c r="E105" t="s">
-        <v>434</v>
+        <v>234</v>
       </c>
       <c r="F105">
         <v>9000000</v>
       </c>
       <c r="G105" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H105">
         <v>35000000</v>
@@ -7213,23 +6631,23 @@
       <c r="A106" t="s">
         <v>120</v>
       </c>
-      <c r="B106" t="s">
-        <v>320</v>
+      <c r="B106">
+        <v>96312724391</v>
       </c>
       <c r="C106">
         <v>25</v>
       </c>
       <c r="D106" t="s">
-        <v>423</v>
+        <v>223</v>
       </c>
       <c r="E106" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F106">
         <v>14000000</v>
       </c>
       <c r="G106" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H106">
         <v>15000000</v>
@@ -7266,23 +6684,23 @@
       <c r="A107" t="s">
         <v>121</v>
       </c>
-      <c r="B107" t="s">
-        <v>321</v>
+      <c r="B107">
+        <v>64877723145</v>
       </c>
       <c r="C107">
         <v>54</v>
       </c>
       <c r="D107" t="s">
-        <v>421</v>
+        <v>221</v>
       </c>
       <c r="E107" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F107">
         <v>28000000</v>
       </c>
       <c r="G107" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H107">
         <v>40000000</v>
@@ -7319,23 +6737,23 @@
       <c r="A108" t="s">
         <v>122</v>
       </c>
-      <c r="B108" t="s">
-        <v>322</v>
+      <c r="B108">
+        <v>61388660706</v>
       </c>
       <c r="C108">
         <v>44</v>
       </c>
       <c r="D108" t="s">
-        <v>430</v>
+        <v>230</v>
       </c>
       <c r="E108" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F108">
         <v>16000000</v>
       </c>
       <c r="G108" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H108">
         <v>40000000</v>
@@ -7372,23 +6790,23 @@
       <c r="A109" t="s">
         <v>123</v>
       </c>
-      <c r="B109" t="s">
-        <v>323</v>
+      <c r="B109">
+        <v>3557373622</v>
       </c>
       <c r="C109">
         <v>37</v>
       </c>
       <c r="D109" t="s">
-        <v>421</v>
+        <v>221</v>
       </c>
       <c r="E109" t="s">
-        <v>434</v>
+        <v>234</v>
       </c>
       <c r="F109">
         <v>15000000</v>
       </c>
       <c r="G109" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H109">
         <v>35000000</v>
@@ -7425,23 +6843,23 @@
       <c r="A110" t="s">
         <v>124</v>
       </c>
-      <c r="B110" t="s">
-        <v>324</v>
+      <c r="B110">
+        <v>5638094737</v>
       </c>
       <c r="C110">
         <v>24</v>
       </c>
       <c r="D110" t="s">
-        <v>421</v>
+        <v>221</v>
       </c>
       <c r="E110" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F110">
         <v>20000000</v>
       </c>
       <c r="G110" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H110">
         <v>35000000</v>
@@ -7478,26 +6896,32 @@
       <c r="A111" t="s">
         <v>125</v>
       </c>
-      <c r="B111" t="s">
-        <v>325</v>
+      <c r="B111">
+        <v>63273780372</v>
       </c>
       <c r="C111">
         <v>19</v>
       </c>
       <c r="D111" t="s">
-        <v>428</v>
+        <v>228</v>
       </c>
       <c r="E111" t="s">
-        <v>433</v>
+        <v>233</v>
       </c>
       <c r="F111">
         <v>4000000</v>
       </c>
       <c r="G111" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H111">
         <v>30000000</v>
+      </c>
+      <c r="I111">
+        <v>0</v>
+      </c>
+      <c r="J111">
+        <v>0</v>
       </c>
       <c r="K111">
         <v>0</v>
@@ -7525,23 +6949,23 @@
       <c r="A112" t="s">
         <v>126</v>
       </c>
-      <c r="B112" t="s">
-        <v>326</v>
+      <c r="B112">
+        <v>21638170736</v>
       </c>
       <c r="C112">
         <v>35</v>
       </c>
       <c r="D112" t="s">
-        <v>429</v>
+        <v>229</v>
       </c>
       <c r="E112" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F112">
         <v>5000000</v>
       </c>
       <c r="G112" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H112">
         <v>10000000</v>
@@ -7578,23 +7002,23 @@
       <c r="A113" t="s">
         <v>127</v>
       </c>
-      <c r="B113" t="s">
-        <v>327</v>
+      <c r="B113">
+        <v>32894543008</v>
       </c>
       <c r="C113">
         <v>48</v>
       </c>
       <c r="D113" t="s">
-        <v>417</v>
+        <v>217</v>
       </c>
       <c r="E113" t="s">
-        <v>434</v>
+        <v>234</v>
       </c>
       <c r="F113">
         <v>23000000</v>
       </c>
       <c r="G113" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H113">
         <v>15000000</v>
@@ -7631,23 +7055,23 @@
       <c r="A114" t="s">
         <v>128</v>
       </c>
-      <c r="B114" t="s">
-        <v>328</v>
+      <c r="B114">
+        <v>14162938468</v>
       </c>
       <c r="C114">
         <v>39</v>
       </c>
       <c r="D114" t="s">
-        <v>426</v>
+        <v>226</v>
       </c>
       <c r="E114" t="s">
-        <v>434</v>
+        <v>234</v>
       </c>
       <c r="F114">
         <v>20000000</v>
       </c>
       <c r="G114" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H114">
         <v>15000000</v>
@@ -7684,23 +7108,23 @@
       <c r="A115" t="s">
         <v>129</v>
       </c>
-      <c r="B115" t="s">
-        <v>329</v>
+      <c r="B115">
+        <v>74257218539</v>
       </c>
       <c r="C115">
         <v>29</v>
       </c>
       <c r="D115" t="s">
-        <v>416</v>
+        <v>216</v>
       </c>
       <c r="E115" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F115">
         <v>9000000</v>
       </c>
       <c r="G115" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H115">
         <v>35000000</v>
@@ -7737,23 +7161,23 @@
       <c r="A116" t="s">
         <v>130</v>
       </c>
-      <c r="B116" t="s">
-        <v>330</v>
+      <c r="B116">
+        <v>61998946672</v>
       </c>
       <c r="C116">
         <v>43</v>
       </c>
       <c r="D116" t="s">
-        <v>426</v>
+        <v>226</v>
       </c>
       <c r="E116" t="s">
-        <v>433</v>
+        <v>233</v>
       </c>
       <c r="F116">
         <v>13000000</v>
       </c>
       <c r="G116" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H116">
         <v>10000000</v>
@@ -7790,23 +7214,23 @@
       <c r="A117" t="s">
         <v>131</v>
       </c>
-      <c r="B117" t="s">
-        <v>331</v>
+      <c r="B117">
+        <v>44611350615</v>
       </c>
       <c r="C117">
         <v>41</v>
       </c>
       <c r="D117" t="s">
-        <v>416</v>
+        <v>216</v>
       </c>
       <c r="E117" t="s">
-        <v>433</v>
+        <v>233</v>
       </c>
       <c r="F117">
         <v>14000000</v>
       </c>
       <c r="G117" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H117">
         <v>35000000</v>
@@ -7843,23 +7267,23 @@
       <c r="A118" t="s">
         <v>132</v>
       </c>
-      <c r="B118" t="s">
-        <v>332</v>
+      <c r="B118">
+        <v>34995099046</v>
       </c>
       <c r="C118">
         <v>43</v>
       </c>
       <c r="D118" t="s">
-        <v>419</v>
+        <v>219</v>
       </c>
       <c r="E118" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F118">
         <v>17000000</v>
       </c>
       <c r="G118" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H118">
         <v>10000000</v>
@@ -7896,26 +7320,32 @@
       <c r="A119" t="s">
         <v>133</v>
       </c>
-      <c r="B119" t="s">
-        <v>333</v>
+      <c r="B119">
+        <v>80981216131</v>
       </c>
       <c r="C119">
         <v>17</v>
       </c>
       <c r="D119" t="s">
-        <v>426</v>
+        <v>226</v>
       </c>
       <c r="E119" t="s">
-        <v>433</v>
+        <v>233</v>
       </c>
       <c r="F119">
         <v>3000000</v>
       </c>
       <c r="G119" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H119">
         <v>25000000</v>
+      </c>
+      <c r="I119">
+        <v>0</v>
+      </c>
+      <c r="J119">
+        <v>0</v>
       </c>
       <c r="K119">
         <v>0</v>
@@ -7943,23 +7373,23 @@
       <c r="A120" t="s">
         <v>134</v>
       </c>
-      <c r="B120" t="s">
-        <v>334</v>
+      <c r="B120">
+        <v>76647470762</v>
       </c>
       <c r="C120">
         <v>42</v>
       </c>
       <c r="D120" t="s">
-        <v>416</v>
+        <v>216</v>
       </c>
       <c r="E120" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F120">
         <v>38000000</v>
       </c>
       <c r="G120" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H120">
         <v>10000000</v>
@@ -7996,23 +7426,23 @@
       <c r="A121" t="s">
         <v>135</v>
       </c>
-      <c r="B121" t="s">
-        <v>335</v>
+      <c r="B121">
+        <v>13455711187</v>
       </c>
       <c r="C121">
         <v>47</v>
       </c>
       <c r="D121" t="s">
-        <v>426</v>
+        <v>226</v>
       </c>
       <c r="E121" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F121">
         <v>18000000</v>
       </c>
       <c r="G121" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H121">
         <v>35000000</v>
@@ -8049,23 +7479,23 @@
       <c r="A122" t="s">
         <v>136</v>
       </c>
-      <c r="B122" t="s">
-        <v>336</v>
+      <c r="B122">
+        <v>40463018962</v>
       </c>
       <c r="C122">
         <v>53</v>
       </c>
       <c r="D122" t="s">
-        <v>428</v>
+        <v>228</v>
       </c>
       <c r="E122" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F122">
         <v>14000000</v>
       </c>
       <c r="G122" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H122">
         <v>20000000</v>
@@ -8102,23 +7532,23 @@
       <c r="A123" t="s">
         <v>137</v>
       </c>
-      <c r="B123" t="s">
-        <v>337</v>
+      <c r="B123">
+        <v>89584969951</v>
       </c>
       <c r="C123">
         <v>44</v>
       </c>
       <c r="D123" t="s">
-        <v>416</v>
+        <v>216</v>
       </c>
       <c r="E123" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F123">
         <v>9000000</v>
       </c>
       <c r="G123" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H123">
         <v>15000000</v>
@@ -8155,23 +7585,23 @@
       <c r="A124" t="s">
         <v>138</v>
       </c>
-      <c r="B124" t="s">
-        <v>338</v>
+      <c r="B124">
+        <v>77675325305</v>
       </c>
       <c r="C124">
         <v>49</v>
       </c>
       <c r="D124" t="s">
-        <v>417</v>
+        <v>217</v>
       </c>
       <c r="E124" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F124">
         <v>10000000</v>
       </c>
       <c r="G124" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H124">
         <v>15000000</v>
@@ -8208,23 +7638,23 @@
       <c r="A125" t="s">
         <v>139</v>
       </c>
-      <c r="B125" t="s">
-        <v>339</v>
+      <c r="B125">
+        <v>53783970194</v>
       </c>
       <c r="C125">
         <v>28</v>
       </c>
       <c r="D125" t="s">
-        <v>429</v>
+        <v>229</v>
       </c>
       <c r="E125" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F125">
         <v>5000000</v>
       </c>
       <c r="G125" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H125">
         <v>15000000</v>
@@ -8261,23 +7691,23 @@
       <c r="A126" t="s">
         <v>140</v>
       </c>
-      <c r="B126" t="s">
-        <v>340</v>
+      <c r="B126">
+        <v>61206059510</v>
       </c>
       <c r="C126">
         <v>31</v>
       </c>
       <c r="D126" t="s">
-        <v>430</v>
+        <v>230</v>
       </c>
       <c r="E126" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F126">
         <v>21000000</v>
       </c>
       <c r="G126" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H126">
         <v>20000000</v>
@@ -8314,23 +7744,23 @@
       <c r="A127" t="s">
         <v>141</v>
       </c>
-      <c r="B127" t="s">
-        <v>341</v>
+      <c r="B127">
+        <v>78508412451</v>
       </c>
       <c r="C127">
         <v>24</v>
       </c>
       <c r="D127" t="s">
-        <v>426</v>
+        <v>226</v>
       </c>
       <c r="E127" t="s">
-        <v>434</v>
+        <v>234</v>
       </c>
       <c r="F127">
         <v>22000000</v>
       </c>
       <c r="G127" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H127">
         <v>15000000</v>
@@ -8367,23 +7797,23 @@
       <c r="A128" t="s">
         <v>142</v>
       </c>
-      <c r="B128" t="s">
-        <v>342</v>
+      <c r="B128">
+        <v>28809013564</v>
       </c>
       <c r="C128">
         <v>36</v>
       </c>
       <c r="D128" t="s">
-        <v>424</v>
+        <v>224</v>
       </c>
       <c r="E128" t="s">
-        <v>434</v>
+        <v>234</v>
       </c>
       <c r="F128">
         <v>7000000</v>
       </c>
       <c r="G128" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H128">
         <v>30000000</v>
@@ -8420,23 +7850,23 @@
       <c r="A129" t="s">
         <v>143</v>
       </c>
-      <c r="B129" t="s">
-        <v>343</v>
+      <c r="B129">
+        <v>70388198918</v>
       </c>
       <c r="C129">
         <v>43</v>
       </c>
       <c r="D129" t="s">
-        <v>431</v>
+        <v>231</v>
       </c>
       <c r="E129" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F129">
         <v>11000000</v>
       </c>
       <c r="G129" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H129">
         <v>40000000</v>
@@ -8473,23 +7903,23 @@
       <c r="A130" t="s">
         <v>144</v>
       </c>
-      <c r="B130" t="s">
-        <v>344</v>
+      <c r="B130">
+        <v>22771461180</v>
       </c>
       <c r="C130">
         <v>52</v>
       </c>
       <c r="D130" t="s">
-        <v>429</v>
+        <v>229</v>
       </c>
       <c r="E130" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F130">
         <v>20000000</v>
       </c>
       <c r="G130" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H130">
         <v>10000000</v>
@@ -8526,23 +7956,23 @@
       <c r="A131" t="s">
         <v>145</v>
       </c>
-      <c r="B131" t="s">
-        <v>345</v>
+      <c r="B131">
+        <v>91192544947</v>
       </c>
       <c r="C131">
         <v>27</v>
       </c>
       <c r="D131" t="s">
-        <v>430</v>
+        <v>230</v>
       </c>
       <c r="E131" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F131">
         <v>13000000</v>
       </c>
       <c r="G131" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H131">
         <v>10000000</v>
@@ -8579,23 +8009,23 @@
       <c r="A132" t="s">
         <v>146</v>
       </c>
-      <c r="B132" t="s">
-        <v>346</v>
+      <c r="B132">
+        <v>28290594946</v>
       </c>
       <c r="C132">
         <v>26</v>
       </c>
       <c r="D132" t="s">
-        <v>420</v>
+        <v>220</v>
       </c>
       <c r="E132" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F132">
         <v>14000000</v>
       </c>
       <c r="G132" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H132">
         <v>40000000</v>
@@ -8632,23 +8062,23 @@
       <c r="A133" t="s">
         <v>147</v>
       </c>
-      <c r="B133" t="s">
-        <v>347</v>
+      <c r="B133">
+        <v>3667820806</v>
       </c>
       <c r="C133">
         <v>70</v>
       </c>
       <c r="D133" t="s">
-        <v>428</v>
+        <v>228</v>
       </c>
       <c r="E133" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F133">
         <v>23000000</v>
       </c>
       <c r="G133" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H133">
         <v>15000000</v>
@@ -8685,23 +8115,23 @@
       <c r="A134" t="s">
         <v>148</v>
       </c>
-      <c r="B134" t="s">
-        <v>348</v>
+      <c r="B134">
+        <v>41238178391</v>
       </c>
       <c r="C134">
         <v>31</v>
       </c>
       <c r="D134" t="s">
-        <v>416</v>
+        <v>216</v>
       </c>
       <c r="E134" t="s">
-        <v>433</v>
+        <v>233</v>
       </c>
       <c r="F134">
         <v>27000000</v>
       </c>
       <c r="G134" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H134">
         <v>35000000</v>
@@ -8738,26 +8168,32 @@
       <c r="A135" t="s">
         <v>149</v>
       </c>
-      <c r="B135" t="s">
-        <v>349</v>
+      <c r="B135">
+        <v>28405291306</v>
       </c>
       <c r="C135">
         <v>18</v>
       </c>
       <c r="D135" t="s">
-        <v>423</v>
+        <v>223</v>
       </c>
       <c r="E135" t="s">
-        <v>433</v>
+        <v>233</v>
       </c>
       <c r="F135">
         <v>5000000</v>
       </c>
       <c r="G135" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H135">
         <v>30000000</v>
+      </c>
+      <c r="I135">
+        <v>0</v>
+      </c>
+      <c r="J135">
+        <v>0</v>
       </c>
       <c r="K135">
         <v>0</v>
@@ -8785,23 +8221,23 @@
       <c r="A136" t="s">
         <v>150</v>
       </c>
-      <c r="B136" t="s">
-        <v>350</v>
+      <c r="B136">
+        <v>43996479451</v>
       </c>
       <c r="C136">
         <v>34</v>
       </c>
       <c r="D136" t="s">
-        <v>431</v>
+        <v>231</v>
       </c>
       <c r="E136" t="s">
-        <v>434</v>
+        <v>234</v>
       </c>
       <c r="F136">
         <v>19000000</v>
       </c>
       <c r="G136" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H136">
         <v>25000000</v>
@@ -8838,23 +8274,23 @@
       <c r="A137" t="s">
         <v>151</v>
       </c>
-      <c r="B137" t="s">
-        <v>351</v>
+      <c r="B137">
+        <v>63641797266</v>
       </c>
       <c r="C137">
         <v>47</v>
       </c>
       <c r="D137" t="s">
-        <v>422</v>
+        <v>222</v>
       </c>
       <c r="E137" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F137">
         <v>4000000</v>
       </c>
       <c r="G137" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H137">
         <v>30000000</v>
@@ -8891,23 +8327,23 @@
       <c r="A138" t="s">
         <v>152</v>
       </c>
-      <c r="B138" t="s">
-        <v>352</v>
+      <c r="B138">
+        <v>63488751094</v>
       </c>
       <c r="C138">
         <v>48</v>
       </c>
       <c r="D138" t="s">
-        <v>423</v>
+        <v>223</v>
       </c>
       <c r="E138" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F138">
         <v>49000000</v>
       </c>
       <c r="G138" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H138">
         <v>40000000</v>
@@ -8944,26 +8380,32 @@
       <c r="A139" t="s">
         <v>153</v>
       </c>
-      <c r="B139" t="s">
-        <v>353</v>
+      <c r="B139">
+        <v>30471032736</v>
       </c>
       <c r="C139">
         <v>19</v>
       </c>
       <c r="D139" t="s">
-        <v>425</v>
+        <v>225</v>
       </c>
       <c r="E139" t="s">
-        <v>433</v>
+        <v>233</v>
       </c>
       <c r="F139">
         <v>4000000</v>
       </c>
       <c r="G139" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H139">
         <v>40000000</v>
+      </c>
+      <c r="I139">
+        <v>0</v>
+      </c>
+      <c r="J139">
+        <v>0</v>
       </c>
       <c r="K139">
         <v>0</v>
@@ -8991,23 +8433,23 @@
       <c r="A140" t="s">
         <v>154</v>
       </c>
-      <c r="B140" t="s">
-        <v>354</v>
+      <c r="B140">
+        <v>74994170269</v>
       </c>
       <c r="C140">
         <v>55</v>
       </c>
       <c r="D140" t="s">
-        <v>426</v>
+        <v>226</v>
       </c>
       <c r="E140" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F140">
         <v>21000000</v>
       </c>
       <c r="G140" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H140">
         <v>40000000</v>
@@ -9044,23 +8486,23 @@
       <c r="A141" t="s">
         <v>155</v>
       </c>
-      <c r="B141" t="s">
-        <v>355</v>
+      <c r="B141">
+        <v>79964499783</v>
       </c>
       <c r="C141">
         <v>25</v>
       </c>
       <c r="D141" t="s">
-        <v>422</v>
+        <v>222</v>
       </c>
       <c r="E141" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F141">
         <v>18000000</v>
       </c>
       <c r="G141" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H141">
         <v>35000000</v>
@@ -9097,23 +8539,23 @@
       <c r="A142" t="s">
         <v>156</v>
       </c>
-      <c r="B142" t="s">
-        <v>356</v>
+      <c r="B142">
+        <v>18579166430</v>
       </c>
       <c r="C142">
         <v>55</v>
       </c>
       <c r="D142" t="s">
-        <v>417</v>
+        <v>217</v>
       </c>
       <c r="E142" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F142">
         <v>40000000</v>
       </c>
       <c r="G142" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H142">
         <v>25000000</v>
@@ -9150,23 +8592,23 @@
       <c r="A143" t="s">
         <v>157</v>
       </c>
-      <c r="B143" t="s">
-        <v>357</v>
+      <c r="B143">
+        <v>88718516880</v>
       </c>
       <c r="C143">
         <v>24</v>
       </c>
       <c r="D143" t="s">
-        <v>424</v>
+        <v>224</v>
       </c>
       <c r="E143" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F143">
         <v>15000000</v>
       </c>
       <c r="G143" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H143">
         <v>25000000</v>
@@ -9203,26 +8645,32 @@
       <c r="A144" t="s">
         <v>158</v>
       </c>
-      <c r="B144" t="s">
-        <v>358</v>
+      <c r="B144">
+        <v>54260743757</v>
       </c>
       <c r="C144">
         <v>19</v>
       </c>
       <c r="D144" t="s">
-        <v>428</v>
+        <v>228</v>
       </c>
       <c r="E144" t="s">
-        <v>433</v>
+        <v>233</v>
       </c>
       <c r="F144">
         <v>4000000</v>
       </c>
       <c r="G144" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H144">
         <v>30000000</v>
+      </c>
+      <c r="I144">
+        <v>0</v>
+      </c>
+      <c r="J144">
+        <v>0</v>
       </c>
       <c r="K144">
         <v>0</v>
@@ -9250,23 +8698,23 @@
       <c r="A145" t="s">
         <v>159</v>
       </c>
-      <c r="B145" t="s">
-        <v>359</v>
+      <c r="B145">
+        <v>73760416009</v>
       </c>
       <c r="C145">
         <v>27</v>
       </c>
       <c r="D145" t="s">
-        <v>418</v>
+        <v>218</v>
       </c>
       <c r="E145" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F145">
         <v>37000000</v>
       </c>
       <c r="G145" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H145">
         <v>35000000</v>
@@ -9303,23 +8751,23 @@
       <c r="A146" t="s">
         <v>160</v>
       </c>
-      <c r="B146" t="s">
-        <v>360</v>
+      <c r="B146">
+        <v>61321009434</v>
       </c>
       <c r="C146">
         <v>25</v>
       </c>
       <c r="D146" t="s">
-        <v>430</v>
+        <v>230</v>
       </c>
       <c r="E146" t="s">
-        <v>433</v>
+        <v>233</v>
       </c>
       <c r="F146">
         <v>16000000</v>
       </c>
       <c r="G146" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H146">
         <v>25000000</v>
@@ -9356,23 +8804,23 @@
       <c r="A147" t="s">
         <v>161</v>
       </c>
-      <c r="B147" t="s">
-        <v>361</v>
+      <c r="B147">
+        <v>50110846676</v>
       </c>
       <c r="C147">
         <v>48</v>
       </c>
       <c r="D147" t="s">
-        <v>417</v>
+        <v>217</v>
       </c>
       <c r="E147" t="s">
-        <v>434</v>
+        <v>234</v>
       </c>
       <c r="F147">
         <v>16000000</v>
       </c>
       <c r="G147" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H147">
         <v>10000000</v>
@@ -9409,23 +8857,23 @@
       <c r="A148" t="s">
         <v>162</v>
       </c>
-      <c r="B148" t="s">
-        <v>362</v>
+      <c r="B148">
+        <v>41674347243</v>
       </c>
       <c r="C148">
         <v>40</v>
       </c>
       <c r="D148" t="s">
-        <v>420</v>
+        <v>220</v>
       </c>
       <c r="E148" t="s">
-        <v>434</v>
+        <v>234</v>
       </c>
       <c r="F148">
         <v>16000000</v>
       </c>
       <c r="G148" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H148">
         <v>25000000</v>
@@ -9462,23 +8910,23 @@
       <c r="A149" t="s">
         <v>163</v>
       </c>
-      <c r="B149" t="s">
-        <v>363</v>
+      <c r="B149">
+        <v>36972997914</v>
       </c>
       <c r="C149">
         <v>36</v>
       </c>
       <c r="D149" t="s">
-        <v>419</v>
+        <v>219</v>
       </c>
       <c r="E149" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F149">
         <v>25000000</v>
       </c>
       <c r="G149" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H149">
         <v>15000000</v>
@@ -9515,23 +8963,23 @@
       <c r="A150" t="s">
         <v>164</v>
       </c>
-      <c r="B150" t="s">
-        <v>364</v>
+      <c r="B150">
+        <v>25723633930</v>
       </c>
       <c r="C150">
         <v>55</v>
       </c>
       <c r="D150" t="s">
-        <v>425</v>
+        <v>225</v>
       </c>
       <c r="E150" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F150">
         <v>19000000</v>
       </c>
       <c r="G150" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H150">
         <v>20000000</v>
@@ -9568,23 +9016,23 @@
       <c r="A151" t="s">
         <v>165</v>
       </c>
-      <c r="B151" t="s">
-        <v>365</v>
+      <c r="B151">
+        <v>33122992171</v>
       </c>
       <c r="C151">
         <v>47</v>
       </c>
       <c r="D151" t="s">
-        <v>427</v>
+        <v>227</v>
       </c>
       <c r="E151" t="s">
-        <v>434</v>
+        <v>234</v>
       </c>
       <c r="F151">
         <v>20000000</v>
       </c>
       <c r="G151" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H151">
         <v>30000000</v>
@@ -9621,23 +9069,23 @@
       <c r="A152" t="s">
         <v>166</v>
       </c>
-      <c r="B152" t="s">
-        <v>366</v>
+      <c r="B152">
+        <v>26237421120</v>
       </c>
       <c r="C152">
         <v>46</v>
       </c>
       <c r="D152" t="s">
-        <v>428</v>
+        <v>228</v>
       </c>
       <c r="E152" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F152">
         <v>5000000</v>
       </c>
       <c r="G152" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H152">
         <v>25000000</v>
@@ -9674,23 +9122,23 @@
       <c r="A153" t="s">
         <v>167</v>
       </c>
-      <c r="B153" t="s">
-        <v>367</v>
+      <c r="B153">
+        <v>30395830755</v>
       </c>
       <c r="C153">
         <v>48</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>216</v>
       </c>
       <c r="E153" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F153">
         <v>19000000</v>
       </c>
       <c r="G153" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H153">
         <v>20000000</v>
@@ -9727,23 +9175,23 @@
       <c r="A154" t="s">
         <v>168</v>
       </c>
-      <c r="B154" t="s">
-        <v>368</v>
+      <c r="B154">
+        <v>50780851356</v>
       </c>
       <c r="C154">
         <v>51</v>
       </c>
       <c r="D154" t="s">
-        <v>429</v>
+        <v>229</v>
       </c>
       <c r="E154" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F154">
         <v>25000000</v>
       </c>
       <c r="G154" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H154">
         <v>15000000</v>
@@ -9780,23 +9228,23 @@
       <c r="A155" t="s">
         <v>169</v>
       </c>
-      <c r="B155" t="s">
-        <v>369</v>
+      <c r="B155">
+        <v>36500443984</v>
       </c>
       <c r="C155">
         <v>41</v>
       </c>
       <c r="D155" t="s">
-        <v>422</v>
+        <v>222</v>
       </c>
       <c r="E155" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F155">
         <v>13000000</v>
       </c>
       <c r="G155" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H155">
         <v>25000000</v>
@@ -9833,23 +9281,23 @@
       <c r="A156" t="s">
         <v>170</v>
       </c>
-      <c r="B156" t="s">
-        <v>370</v>
+      <c r="B156">
+        <v>71986819856</v>
       </c>
       <c r="C156">
         <v>49</v>
       </c>
       <c r="D156" t="s">
-        <v>424</v>
+        <v>224</v>
       </c>
       <c r="E156" t="s">
-        <v>434</v>
+        <v>234</v>
       </c>
       <c r="F156">
         <v>12000000</v>
       </c>
       <c r="G156" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H156">
         <v>25000000</v>
@@ -9886,23 +9334,23 @@
       <c r="A157" t="s">
         <v>171</v>
       </c>
-      <c r="B157" t="s">
-        <v>371</v>
+      <c r="B157">
+        <v>32577650961</v>
       </c>
       <c r="C157">
         <v>55</v>
       </c>
       <c r="D157" t="s">
-        <v>416</v>
+        <v>216</v>
       </c>
       <c r="E157" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F157">
         <v>49000000</v>
       </c>
       <c r="G157" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H157">
         <v>15000000</v>
@@ -9939,23 +9387,23 @@
       <c r="A158" t="s">
         <v>172</v>
       </c>
-      <c r="B158" t="s">
-        <v>372</v>
+      <c r="B158">
+        <v>50419696050</v>
       </c>
       <c r="C158">
         <v>35</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>221</v>
       </c>
       <c r="E158" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F158">
         <v>24000000</v>
       </c>
       <c r="G158" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H158">
         <v>15000000</v>
@@ -9992,23 +9440,23 @@
       <c r="A159" t="s">
         <v>173</v>
       </c>
-      <c r="B159" t="s">
-        <v>373</v>
+      <c r="B159">
+        <v>94314619798</v>
       </c>
       <c r="C159">
         <v>47</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>221</v>
       </c>
       <c r="E159" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F159">
         <v>17000000</v>
       </c>
       <c r="G159" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H159">
         <v>25000000</v>
@@ -10045,23 +9493,23 @@
       <c r="A160" t="s">
         <v>174</v>
       </c>
-      <c r="B160" t="s">
-        <v>374</v>
+      <c r="B160">
+        <v>17504451704</v>
       </c>
       <c r="C160">
         <v>35</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>223</v>
       </c>
       <c r="E160" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F160">
         <v>4000000</v>
       </c>
       <c r="G160" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H160">
         <v>40000000</v>
@@ -10098,23 +9546,23 @@
       <c r="A161" t="s">
         <v>175</v>
       </c>
-      <c r="B161" t="s">
-        <v>375</v>
+      <c r="B161">
+        <v>34351419330</v>
       </c>
       <c r="C161">
         <v>30</v>
       </c>
       <c r="D161" t="s">
-        <v>417</v>
+        <v>217</v>
       </c>
       <c r="E161" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F161">
         <v>19000000</v>
       </c>
       <c r="G161" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H161">
         <v>30000000</v>
@@ -10151,23 +9599,23 @@
       <c r="A162" t="s">
         <v>176</v>
       </c>
-      <c r="B162" t="s">
-        <v>376</v>
+      <c r="B162">
+        <v>98935673556</v>
       </c>
       <c r="C162">
         <v>40</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>224</v>
       </c>
       <c r="E162" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F162">
         <v>24000000</v>
       </c>
       <c r="G162" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H162">
         <v>30000000</v>
@@ -10204,23 +9652,23 @@
       <c r="A163" t="s">
         <v>177</v>
       </c>
-      <c r="B163" t="s">
-        <v>377</v>
+      <c r="B163">
+        <v>9934358005</v>
       </c>
       <c r="C163">
         <v>38</v>
       </c>
       <c r="D163" t="s">
-        <v>431</v>
+        <v>231</v>
       </c>
       <c r="E163" t="s">
-        <v>433</v>
+        <v>233</v>
       </c>
       <c r="F163">
         <v>12000000</v>
       </c>
       <c r="G163" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H163">
         <v>30000000</v>
@@ -10257,23 +9705,23 @@
       <c r="A164" t="s">
         <v>178</v>
       </c>
-      <c r="B164" t="s">
-        <v>378</v>
+      <c r="B164">
+        <v>9776766620</v>
       </c>
       <c r="C164">
         <v>55</v>
       </c>
       <c r="D164" t="s">
-        <v>420</v>
+        <v>220</v>
       </c>
       <c r="E164" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F164">
         <v>39000000</v>
       </c>
       <c r="G164" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H164">
         <v>10000000</v>
@@ -10310,23 +9758,23 @@
       <c r="A165" t="s">
         <v>179</v>
       </c>
-      <c r="B165" t="s">
-        <v>379</v>
+      <c r="B165">
+        <v>42781275410</v>
       </c>
       <c r="C165">
         <v>47</v>
       </c>
       <c r="D165" t="s">
-        <v>418</v>
+        <v>218</v>
       </c>
       <c r="E165" t="s">
-        <v>434</v>
+        <v>234</v>
       </c>
       <c r="F165">
         <v>6000000</v>
       </c>
       <c r="G165" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H165">
         <v>15000000</v>
@@ -10363,23 +9811,23 @@
       <c r="A166" t="s">
         <v>180</v>
       </c>
-      <c r="B166" t="s">
-        <v>380</v>
+      <c r="B166">
+        <v>25972794419</v>
       </c>
       <c r="C166">
         <v>49</v>
       </c>
       <c r="D166" t="s">
-        <v>421</v>
+        <v>221</v>
       </c>
       <c r="E166" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F166">
         <v>45000000</v>
       </c>
       <c r="G166" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H166">
         <v>15000000</v>
@@ -10416,23 +9864,23 @@
       <c r="A167" t="s">
         <v>181</v>
       </c>
-      <c r="B167" t="s">
-        <v>381</v>
+      <c r="B167">
+        <v>93203667447</v>
       </c>
       <c r="C167">
         <v>42</v>
       </c>
       <c r="D167" t="s">
-        <v>419</v>
+        <v>219</v>
       </c>
       <c r="E167" t="s">
-        <v>434</v>
+        <v>234</v>
       </c>
       <c r="F167">
         <v>17000000</v>
       </c>
       <c r="G167" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H167">
         <v>25000000</v>
@@ -10469,23 +9917,23 @@
       <c r="A168" t="s">
         <v>182</v>
       </c>
-      <c r="B168" t="s">
-        <v>382</v>
+      <c r="B168">
+        <v>11943346286</v>
       </c>
       <c r="C168">
         <v>52</v>
       </c>
       <c r="D168" t="s">
-        <v>421</v>
+        <v>221</v>
       </c>
       <c r="E168" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F168">
         <v>9000000</v>
       </c>
       <c r="G168" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H168">
         <v>35000000</v>
@@ -10522,23 +9970,23 @@
       <c r="A169" t="s">
         <v>183</v>
       </c>
-      <c r="B169" t="s">
-        <v>383</v>
+      <c r="B169">
+        <v>47930121873</v>
       </c>
       <c r="C169">
         <v>26</v>
       </c>
       <c r="D169" t="s">
-        <v>418</v>
+        <v>218</v>
       </c>
       <c r="E169" t="s">
-        <v>433</v>
+        <v>233</v>
       </c>
       <c r="F169">
         <v>14000000</v>
       </c>
       <c r="G169" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H169">
         <v>30000000</v>
@@ -10575,23 +10023,23 @@
       <c r="A170" t="s">
         <v>184</v>
       </c>
-      <c r="B170" t="s">
-        <v>384</v>
+      <c r="B170">
+        <v>47734745167</v>
       </c>
       <c r="C170">
         <v>26</v>
       </c>
       <c r="D170" t="s">
-        <v>421</v>
+        <v>221</v>
       </c>
       <c r="E170" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F170">
         <v>29000000</v>
       </c>
       <c r="G170" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H170">
         <v>20000000</v>
@@ -10628,23 +10076,23 @@
       <c r="A171" t="s">
         <v>185</v>
       </c>
-      <c r="B171" t="s">
-        <v>385</v>
+      <c r="B171">
+        <v>36882455336</v>
       </c>
       <c r="C171">
         <v>38</v>
       </c>
       <c r="D171" t="s">
-        <v>418</v>
+        <v>218</v>
       </c>
       <c r="E171" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F171">
         <v>35000000</v>
       </c>
       <c r="G171" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H171">
         <v>30000000</v>
@@ -10681,23 +10129,23 @@
       <c r="A172" t="s">
         <v>186</v>
       </c>
-      <c r="B172" t="s">
-        <v>386</v>
+      <c r="B172">
+        <v>34723501571</v>
       </c>
       <c r="C172">
         <v>55</v>
       </c>
       <c r="D172" t="s">
-        <v>419</v>
+        <v>219</v>
       </c>
       <c r="E172" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F172">
         <v>22000000</v>
       </c>
       <c r="G172" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H172">
         <v>25000000</v>
@@ -10734,23 +10182,23 @@
       <c r="A173" t="s">
         <v>187</v>
       </c>
-      <c r="B173" t="s">
-        <v>387</v>
+      <c r="B173">
+        <v>55127136780</v>
       </c>
       <c r="C173">
         <v>46</v>
       </c>
       <c r="D173" t="s">
-        <v>418</v>
+        <v>218</v>
       </c>
       <c r="E173" t="s">
-        <v>433</v>
+        <v>233</v>
       </c>
       <c r="F173">
         <v>12000000</v>
       </c>
       <c r="G173" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H173">
         <v>30000000</v>
@@ -10787,23 +10235,23 @@
       <c r="A174" t="s">
         <v>188</v>
       </c>
-      <c r="B174" t="s">
-        <v>388</v>
+      <c r="B174">
+        <v>74683557915</v>
       </c>
       <c r="C174">
         <v>37</v>
       </c>
       <c r="D174" t="s">
-        <v>428</v>
+        <v>228</v>
       </c>
       <c r="E174" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F174">
         <v>56000000</v>
       </c>
       <c r="G174" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H174">
         <v>10000000</v>
@@ -10840,23 +10288,23 @@
       <c r="A175" t="s">
         <v>189</v>
       </c>
-      <c r="B175" t="s">
-        <v>389</v>
+      <c r="B175">
+        <v>19974863158</v>
       </c>
       <c r="C175">
         <v>46</v>
       </c>
       <c r="D175" t="s">
-        <v>430</v>
+        <v>230</v>
       </c>
       <c r="E175" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F175">
         <v>32000000</v>
       </c>
       <c r="G175" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H175">
         <v>10000000</v>
@@ -10893,23 +10341,23 @@
       <c r="A176" t="s">
         <v>190</v>
       </c>
-      <c r="B176" t="s">
-        <v>390</v>
+      <c r="B176">
+        <v>72989325966</v>
       </c>
       <c r="C176">
         <v>34</v>
       </c>
       <c r="D176" t="s">
-        <v>426</v>
+        <v>226</v>
       </c>
       <c r="E176" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F176">
         <v>22000000</v>
       </c>
       <c r="G176" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H176">
         <v>20000000</v>
@@ -10946,23 +10394,23 @@
       <c r="A177" t="s">
         <v>191</v>
       </c>
-      <c r="B177" t="s">
-        <v>391</v>
+      <c r="B177">
+        <v>7452954600</v>
       </c>
       <c r="C177">
         <v>24</v>
       </c>
       <c r="D177" t="s">
-        <v>429</v>
+        <v>229</v>
       </c>
       <c r="E177" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F177">
         <v>31000000</v>
       </c>
       <c r="G177" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H177">
         <v>40000000</v>
@@ -10999,23 +10447,23 @@
       <c r="A178" t="s">
         <v>192</v>
       </c>
-      <c r="B178" t="s">
-        <v>392</v>
+      <c r="B178">
+        <v>29336456636</v>
       </c>
       <c r="C178">
         <v>55</v>
       </c>
       <c r="D178" t="s">
-        <v>424</v>
+        <v>224</v>
       </c>
       <c r="E178" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F178">
         <v>16000000</v>
       </c>
       <c r="G178" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H178">
         <v>35000000</v>
@@ -11052,23 +10500,23 @@
       <c r="A179" t="s">
         <v>193</v>
       </c>
-      <c r="B179" t="s">
-        <v>393</v>
+      <c r="B179">
+        <v>36600035891</v>
       </c>
       <c r="C179">
         <v>44</v>
       </c>
       <c r="D179" t="s">
-        <v>427</v>
+        <v>227</v>
       </c>
       <c r="E179" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F179">
         <v>15000000</v>
       </c>
       <c r="G179" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H179">
         <v>40000000</v>
@@ -11105,23 +10553,23 @@
       <c r="A180" t="s">
         <v>194</v>
       </c>
-      <c r="B180" t="s">
-        <v>394</v>
+      <c r="B180">
+        <v>53868267154</v>
       </c>
       <c r="C180">
         <v>31</v>
       </c>
       <c r="D180" t="s">
-        <v>417</v>
+        <v>217</v>
       </c>
       <c r="E180" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F180">
         <v>51000000</v>
       </c>
       <c r="G180" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H180">
         <v>25000000</v>
@@ -11158,23 +10606,23 @@
       <c r="A181" t="s">
         <v>195</v>
       </c>
-      <c r="B181" t="s">
-        <v>395</v>
+      <c r="B181">
+        <v>28188429108</v>
       </c>
       <c r="C181">
         <v>27</v>
       </c>
       <c r="D181" t="s">
-        <v>421</v>
+        <v>221</v>
       </c>
       <c r="E181" t="s">
-        <v>434</v>
+        <v>234</v>
       </c>
       <c r="F181">
         <v>12000000</v>
       </c>
       <c r="G181" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H181">
         <v>25000000</v>
@@ -11211,23 +10659,23 @@
       <c r="A182" t="s">
         <v>196</v>
       </c>
-      <c r="B182" t="s">
-        <v>396</v>
+      <c r="B182">
+        <v>4234947329</v>
       </c>
       <c r="C182">
         <v>51</v>
       </c>
       <c r="D182" t="s">
-        <v>431</v>
+        <v>231</v>
       </c>
       <c r="E182" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F182">
         <v>4000000</v>
       </c>
       <c r="G182" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H182">
         <v>15000000</v>
@@ -11264,23 +10712,23 @@
       <c r="A183" t="s">
         <v>197</v>
       </c>
-      <c r="B183" t="s">
-        <v>397</v>
+      <c r="B183">
+        <v>4401943791</v>
       </c>
       <c r="C183">
         <v>27</v>
       </c>
       <c r="D183" t="s">
-        <v>430</v>
+        <v>230</v>
       </c>
       <c r="E183" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F183">
         <v>27000000</v>
       </c>
       <c r="G183" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H183">
         <v>10000000</v>
@@ -11317,23 +10765,23 @@
       <c r="A184" t="s">
         <v>198</v>
       </c>
-      <c r="B184" t="s">
-        <v>398</v>
+      <c r="B184">
+        <v>54650660306</v>
       </c>
       <c r="C184">
         <v>31</v>
       </c>
       <c r="D184" t="s">
-        <v>417</v>
+        <v>217</v>
       </c>
       <c r="E184" t="s">
-        <v>433</v>
+        <v>233</v>
       </c>
       <c r="F184">
         <v>24000000</v>
       </c>
       <c r="G184" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H184">
         <v>40000000</v>
@@ -11370,23 +10818,23 @@
       <c r="A185" t="s">
         <v>199</v>
       </c>
-      <c r="B185" t="s">
-        <v>399</v>
+      <c r="B185">
+        <v>90538403877</v>
       </c>
       <c r="C185">
         <v>27</v>
       </c>
       <c r="D185" t="s">
-        <v>427</v>
+        <v>227</v>
       </c>
       <c r="E185" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F185">
         <v>24000000</v>
       </c>
       <c r="G185" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H185">
         <v>15000000</v>
@@ -11423,23 +10871,23 @@
       <c r="A186" t="s">
         <v>200</v>
       </c>
-      <c r="B186" t="s">
-        <v>400</v>
+      <c r="B186">
+        <v>10161758771</v>
       </c>
       <c r="C186">
         <v>46</v>
       </c>
       <c r="D186" t="s">
-        <v>423</v>
+        <v>223</v>
       </c>
       <c r="E186" t="s">
-        <v>434</v>
+        <v>234</v>
       </c>
       <c r="F186">
         <v>9000000</v>
       </c>
       <c r="G186" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H186">
         <v>15000000</v>
@@ -11476,23 +10924,23 @@
       <c r="A187" t="s">
         <v>201</v>
       </c>
-      <c r="B187" t="s">
-        <v>401</v>
+      <c r="B187">
+        <v>43780508727</v>
       </c>
       <c r="C187">
         <v>55</v>
       </c>
       <c r="D187" t="s">
-        <v>422</v>
+        <v>222</v>
       </c>
       <c r="E187" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F187">
         <v>25000000</v>
       </c>
       <c r="G187" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H187">
         <v>30000000</v>
@@ -11529,23 +10977,23 @@
       <c r="A188" t="s">
         <v>202</v>
       </c>
-      <c r="B188" t="s">
-        <v>402</v>
+      <c r="B188">
+        <v>34691600564</v>
       </c>
       <c r="C188">
         <v>47</v>
       </c>
       <c r="D188" t="s">
-        <v>431</v>
+        <v>231</v>
       </c>
       <c r="E188" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F188">
         <v>34000000</v>
       </c>
       <c r="G188" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H188">
         <v>30000000</v>
@@ -11582,23 +11030,23 @@
       <c r="A189" t="s">
         <v>203</v>
       </c>
-      <c r="B189" t="s">
-        <v>403</v>
+      <c r="B189">
+        <v>54711146399</v>
       </c>
       <c r="C189">
         <v>26</v>
       </c>
       <c r="D189" t="s">
-        <v>431</v>
+        <v>231</v>
       </c>
       <c r="E189" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F189">
         <v>22000000</v>
       </c>
       <c r="G189" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H189">
         <v>30000000</v>
@@ -11635,23 +11083,23 @@
       <c r="A190" t="s">
         <v>204</v>
       </c>
-      <c r="B190" t="s">
-        <v>404</v>
+      <c r="B190">
+        <v>26431409147</v>
       </c>
       <c r="C190">
         <v>25</v>
       </c>
       <c r="D190" t="s">
-        <v>430</v>
+        <v>230</v>
       </c>
       <c r="E190" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F190">
         <v>18000000</v>
       </c>
       <c r="G190" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H190">
         <v>15000000</v>
@@ -11688,23 +11136,23 @@
       <c r="A191" t="s">
         <v>205</v>
       </c>
-      <c r="B191" t="s">
-        <v>405</v>
+      <c r="B191">
+        <v>82795255224</v>
       </c>
       <c r="C191">
         <v>49</v>
       </c>
       <c r="D191" t="s">
-        <v>424</v>
+        <v>224</v>
       </c>
       <c r="E191" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F191">
         <v>24000000</v>
       </c>
       <c r="G191" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H191">
         <v>40000000</v>
@@ -11741,23 +11189,23 @@
       <c r="A192" t="s">
         <v>206</v>
       </c>
-      <c r="B192" t="s">
-        <v>406</v>
+      <c r="B192">
+        <v>54678188252</v>
       </c>
       <c r="C192">
         <v>47</v>
       </c>
       <c r="D192" t="s">
-        <v>422</v>
+        <v>222</v>
       </c>
       <c r="E192" t="s">
-        <v>434</v>
+        <v>234</v>
       </c>
       <c r="F192">
         <v>13000000</v>
       </c>
       <c r="G192" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H192">
         <v>30000000</v>
@@ -11794,23 +11242,23 @@
       <c r="A193" t="s">
         <v>207</v>
       </c>
-      <c r="B193" t="s">
-        <v>407</v>
+      <c r="B193">
+        <v>45714342785</v>
       </c>
       <c r="C193">
         <v>51</v>
       </c>
       <c r="D193" t="s">
-        <v>418</v>
+        <v>218</v>
       </c>
       <c r="E193" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F193">
         <v>16000000</v>
       </c>
       <c r="G193" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H193">
         <v>40000000</v>
@@ -11847,23 +11295,23 @@
       <c r="A194" t="s">
         <v>208</v>
       </c>
-      <c r="B194" t="s">
-        <v>408</v>
+      <c r="B194">
+        <v>61362631151</v>
       </c>
       <c r="C194">
         <v>37</v>
       </c>
       <c r="D194" t="s">
-        <v>425</v>
+        <v>225</v>
       </c>
       <c r="E194" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F194">
         <v>29000000</v>
       </c>
       <c r="G194" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H194">
         <v>25000000</v>
@@ -11900,23 +11348,23 @@
       <c r="A195" t="s">
         <v>209</v>
       </c>
-      <c r="B195" t="s">
-        <v>409</v>
+      <c r="B195">
+        <v>32111157492</v>
       </c>
       <c r="C195">
         <v>40</v>
       </c>
       <c r="D195" t="s">
-        <v>425</v>
+        <v>225</v>
       </c>
       <c r="E195" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F195">
         <v>25000000</v>
       </c>
       <c r="G195" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H195">
         <v>25000000</v>
@@ -11953,23 +11401,23 @@
       <c r="A196" t="s">
         <v>210</v>
       </c>
-      <c r="B196" t="s">
-        <v>410</v>
+      <c r="B196">
+        <v>92364564423</v>
       </c>
       <c r="C196">
         <v>41</v>
       </c>
       <c r="D196" t="s">
-        <v>427</v>
+        <v>227</v>
       </c>
       <c r="E196" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F196">
         <v>20000000</v>
       </c>
       <c r="G196" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H196">
         <v>40000000</v>
@@ -12006,23 +11454,23 @@
       <c r="A197" t="s">
         <v>211</v>
       </c>
-      <c r="B197" t="s">
-        <v>411</v>
+      <c r="B197">
+        <v>61653679973</v>
       </c>
       <c r="C197">
         <v>27</v>
       </c>
       <c r="D197" t="s">
-        <v>417</v>
+        <v>217</v>
       </c>
       <c r="E197" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F197">
         <v>22000000</v>
       </c>
       <c r="G197" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H197">
         <v>10000000</v>
@@ -12059,23 +11507,23 @@
       <c r="A198" t="s">
         <v>212</v>
       </c>
-      <c r="B198" t="s">
-        <v>412</v>
+      <c r="B198">
+        <v>65601825146</v>
       </c>
       <c r="C198">
         <v>48</v>
       </c>
       <c r="D198" t="s">
-        <v>430</v>
+        <v>230</v>
       </c>
       <c r="E198" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F198">
         <v>37000000</v>
       </c>
       <c r="G198" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H198">
         <v>20000000</v>
@@ -12112,23 +11560,23 @@
       <c r="A199" t="s">
         <v>213</v>
       </c>
-      <c r="B199" t="s">
-        <v>413</v>
+      <c r="B199">
+        <v>19417521610</v>
       </c>
       <c r="C199">
         <v>43</v>
       </c>
       <c r="D199" t="s">
-        <v>430</v>
+        <v>230</v>
       </c>
       <c r="E199" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F199">
         <v>11000000</v>
       </c>
       <c r="G199" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H199">
         <v>35000000</v>
@@ -12165,23 +11613,23 @@
       <c r="A200" t="s">
         <v>214</v>
       </c>
-      <c r="B200" t="s">
-        <v>414</v>
+      <c r="B200">
+        <v>40943061437</v>
       </c>
       <c r="C200">
         <v>42</v>
       </c>
       <c r="D200" t="s">
-        <v>419</v>
+        <v>219</v>
       </c>
       <c r="E200" t="s">
-        <v>435</v>
+        <v>235</v>
       </c>
       <c r="F200">
         <v>24000000</v>
       </c>
       <c r="G200" t="s">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="H200">
         <v>35000000</v>
@@ -12218,23 +11666,23 @@
       <c r="A201" t="s">
         <v>215</v>
       </c>
-      <c r="B201" t="s">
-        <v>415</v>
+      <c r="B201">
+        <v>77699447068</v>
       </c>
       <c r="C201">
         <v>35</v>
       </c>
       <c r="D201" t="s">
-        <v>416</v>
+        <v>216</v>
       </c>
       <c r="E201" t="s">
-        <v>432</v>
+        <v>232</v>
       </c>
       <c r="F201">
         <v>27000000</v>
       </c>
       <c r="G201" t="s">
-        <v>437</v>
+        <v>237</v>
       </c>
       <c r="H201">
         <v>25000000</v>
